--- a/financial-report-excel-filler/references/财报填充.xlsx
+++ b/financial-report-excel-filler/references/财报填充.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyjie/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0f1953a9d5ec61e/文档/financial_report/financial-report-excel-filler/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FF6260-C262-A04A-A444-05C7F88DB74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{45FF6260-C262-A04A-A444-05C7F88DB74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7600FB-D57E-A64A-AC46-6FEF63E11B4A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="财报及财务指标" sheetId="1" r:id="rId1"/>
     <sheet name="简版财报（使用财务及财务指标sheet里的合并口径数据填充）" sheetId="2" r:id="rId2"/>
+    <sheet name="偿债分析（使用财报及财务指标sheet里的数据填充）" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
   <si>
     <t>科目</t>
   </si>
@@ -346,6 +347,38 @@
   </si>
   <si>
     <t>现金流量</t>
+  </si>
+  <si>
+    <t>合并口径</t>
+  </si>
+  <si>
+    <t>单体口径</t>
+  </si>
+  <si>
+    <t>短期借款</t>
+  </si>
+  <si>
+    <t>短期刚性负债合计</t>
+  </si>
+  <si>
+    <t>长期借款</t>
+  </si>
+  <si>
+    <t>长期刚性负债合计</t>
+  </si>
+  <si>
+    <t>刚性负债合计</t>
+  </si>
+  <si>
+    <t>现金短债比</t>
+  </si>
+  <si>
+    <t>2023年</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>即期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -353,10 +386,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
-    <numFmt numFmtId="181" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -385,6 +418,21 @@
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -569,7 +617,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -579,18 +627,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -645,23 +711,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,6 +744,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -965,25 +1035,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12">
-      <c r="D1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="7" t="s">
+      <c r="D1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="7" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="8"/>
-      <c r="L1" s="9"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="4:12">
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25"/>
       <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
@@ -1007,2111 +1077,2110 @@
       </c>
     </row>
     <row r="3" spans="4:12">
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="7">
         <v>570.97016799999994</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="7">
         <v>567.80291999999997</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="7">
         <v>541.49630300000001</v>
       </c>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25">
+      <c r="I3" s="7"/>
+      <c r="J3" s="7">
         <v>235.721498</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="7">
         <v>254.32077699999999</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="7">
         <v>252.49392900000001</v>
       </c>
     </row>
     <row r="4" spans="4:12">
-      <c r="D4" s="11"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="7">
         <v>215.11788399999998</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="7">
         <v>209.31363200000001</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="7">
         <v>178.64533299999999</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25">
+      <c r="I4" s="7"/>
+      <c r="J4" s="7">
         <v>0.35689899999999997</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="7">
         <v>19.105357999999999</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="7">
         <v>17.45804</v>
       </c>
     </row>
     <row r="5" spans="4:12">
-      <c r="D5" s="11"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="8">
         <v>78.115516</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="8">
         <v>91.077581000000009</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="8">
         <v>65.397556000000009</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
         <v>5.3400999999999997E-2</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="8">
         <v>9.2383000000000007E-2</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="8">
         <v>0.71684499999999995</v>
       </c>
     </row>
     <row r="6" spans="4:12">
-      <c r="D6" s="11"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="8">
         <v>9.9719750000000005</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="8">
         <v>6.0785349999999996</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="8">
         <v>17.670655</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26">
-        <v>0</v>
-      </c>
-      <c r="K6" s="26">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
         <v>3.8587000000000003E-2</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="8">
         <v>0.388654</v>
       </c>
     </row>
     <row r="7" spans="4:12">
-      <c r="D7" s="11"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="8">
         <v>5.0779249999999996</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="8">
         <v>2.9067799999999999</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="8">
         <v>4.7327269999999997</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26">
-        <v>0</v>
-      </c>
-      <c r="K7" s="26">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
         <v>0.78757100000000002</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="8">
         <v>1.5075700000000001</v>
       </c>
     </row>
     <row r="8" spans="4:12">
-      <c r="D8" s="11"/>
+      <c r="D8" s="17"/>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="8">
         <v>0.57736799999999999</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="8">
         <v>0.66803599999999996</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="8">
         <v>1.1283700000000001</v>
       </c>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26">
-        <v>0</v>
-      </c>
-      <c r="K8" s="26">
-        <v>0</v>
-      </c>
-      <c r="L8" s="26">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="4:12">
-      <c r="D9" s="11"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="8">
         <v>20.780946</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="8">
         <v>15.084623000000001</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="8">
         <v>11.601576</v>
       </c>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26">
-        <v>0</v>
-      </c>
-      <c r="K9" s="26">
+      <c r="I9" s="8"/>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
         <v>1.7559880000000001</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="8">
         <v>3.2490000000000002E-3</v>
       </c>
     </row>
     <row r="10" spans="4:12">
-      <c r="D10" s="11"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="8">
         <v>0.96690699999999996</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="8">
         <v>1.257773</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="8">
         <v>1.944834</v>
       </c>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26">
+      <c r="I10" s="8"/>
+      <c r="J10" s="8">
         <v>0.28043400000000002</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="8">
         <v>15.456351999999999</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="8">
         <v>14.805128</v>
       </c>
     </row>
     <row r="11" spans="4:12">
-      <c r="D11" s="11"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="8">
         <v>95.433026999999996</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="8">
         <v>88.23933000000001</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="8">
         <v>71.873268999999993</v>
       </c>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26">
-        <v>0</v>
-      </c>
-      <c r="K11" s="26">
+      <c r="I11" s="8"/>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
         <v>0.94643700000000008</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="4:12" ht="28">
-      <c r="D12" s="11"/>
+      <c r="D12" s="17"/>
       <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="8">
         <v>0.25</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="8">
         <v>0.375</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="8">
         <v>0.34499999999999997</v>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26">
-        <v>0</v>
-      </c>
-      <c r="K12" s="26">
-        <v>0</v>
-      </c>
-      <c r="L12" s="26">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="4:12">
-      <c r="D13" s="11"/>
+      <c r="D13" s="17"/>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="8">
         <v>3.9442199999999996</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="8">
         <v>3.6259739999999998</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="8">
         <v>3.9513470000000002</v>
       </c>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26">
+      <c r="I13" s="8"/>
+      <c r="J13" s="8">
         <v>2.3065000000000002E-2</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="8">
         <v>2.8039999999999999E-2</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="8">
         <v>3.6594000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="4:12">
-      <c r="D14" s="11"/>
+      <c r="D14" s="17"/>
       <c r="E14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="7">
         <v>355.852284</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="7">
         <v>358.48928899999999</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="7">
         <v>362.85096900000002</v>
       </c>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25">
+      <c r="I14" s="7"/>
+      <c r="J14" s="7">
         <v>235.36459900000003</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="7">
         <v>235.215419</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="7">
         <v>235.03588999999999</v>
       </c>
     </row>
     <row r="15" spans="4:12" ht="28">
-      <c r="D15" s="11"/>
+      <c r="D15" s="17"/>
       <c r="E15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="26">
-        <v>0</v>
-      </c>
-      <c r="G15" s="26">
-        <v>0</v>
-      </c>
-      <c r="H15" s="26">
-        <v>0</v>
-      </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26">
-        <v>0</v>
-      </c>
-      <c r="K15" s="26">
-        <v>0</v>
-      </c>
-      <c r="L15" s="26">
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="4:12" ht="28">
-      <c r="D16" s="11"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="26">
-        <v>0</v>
-      </c>
-      <c r="G16" s="26">
-        <v>0</v>
-      </c>
-      <c r="H16" s="26">
-        <v>0</v>
-      </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26">
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8">
         <v>234.67099999999999</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="8">
         <v>234.67099999999999</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="8">
         <v>234.67099999999999</v>
       </c>
     </row>
     <row r="17" spans="4:12">
-      <c r="D17" s="11"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="8">
         <v>0.89600000000000002</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="8">
         <v>0.52100000000000002</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="8">
         <v>0.16</v>
       </c>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26">
-        <v>0</v>
-      </c>
-      <c r="K17" s="26">
-        <v>0</v>
-      </c>
-      <c r="L17" s="26">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="4:12">
-      <c r="D18" s="11"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="8">
         <v>264.67085499999996</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="8">
         <v>273.507092</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="8">
         <v>286.74106499999999</v>
       </c>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8">
         <v>9.6199000000000007E-2</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="8">
         <v>8.1419000000000005E-2</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="8">
         <v>5.5511999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="4:12">
-      <c r="D19" s="11"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="8">
         <v>43.442900999999999</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="8">
         <v>28.618996999999997</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="8">
         <v>18.770126000000001</v>
       </c>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26">
-        <v>0</v>
-      </c>
-      <c r="K19" s="26">
-        <v>0</v>
-      </c>
-      <c r="L19" s="26">
+      <c r="I19" s="8"/>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="4:12">
-      <c r="D20" s="11"/>
+      <c r="D20" s="17"/>
       <c r="E20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="8">
         <v>1.4445E-2</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="8">
         <v>0.11541300000000002</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="8">
         <v>7.3358000000000007E-2</v>
       </c>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26">
-        <v>0</v>
-      </c>
-      <c r="K20" s="26">
-        <v>0</v>
-      </c>
-      <c r="L20" s="26">
+      <c r="I20" s="8"/>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="4:12">
-      <c r="D21" s="11"/>
+      <c r="D21" s="17"/>
       <c r="E21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="26">
-        <v>0</v>
-      </c>
-      <c r="G21" s="26">
-        <v>0</v>
-      </c>
-      <c r="H21" s="26">
-        <v>0</v>
-      </c>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26">
-        <v>0</v>
-      </c>
-      <c r="K21" s="26">
-        <v>0</v>
-      </c>
-      <c r="L21" s="26">
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="4:12">
-      <c r="D22" s="11"/>
+      <c r="D22" s="17"/>
       <c r="E22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="8">
         <v>14.802370999999999</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="8">
         <v>38.363498</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="8">
         <v>38.383371000000004</v>
       </c>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26">
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
         <v>5.6899999999999997E-3</v>
       </c>
-      <c r="K22" s="26">
+      <c r="K22" s="8">
         <v>3.7810000000000001E-3</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="8">
         <v>1.8879999999999999E-3</v>
       </c>
     </row>
     <row r="23" spans="4:12">
-      <c r="D23" s="11"/>
+      <c r="D23" s="17"/>
       <c r="E23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="26">
-        <v>0</v>
-      </c>
-      <c r="G23" s="26">
-        <v>0</v>
-      </c>
-      <c r="H23" s="26">
-        <v>0</v>
-      </c>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26">
-        <v>0</v>
-      </c>
-      <c r="K23" s="26">
-        <v>0</v>
-      </c>
-      <c r="L23" s="26">
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="4:12" ht="28">
-      <c r="D24" s="11"/>
+      <c r="D24" s="17"/>
       <c r="E24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="8">
         <v>4.0090170000000001</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="8">
         <v>5.2695999999999996</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="8">
         <v>6.0426989999999998</v>
       </c>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26">
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
         <v>0.46198400000000001</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="8">
         <v>0.36785100000000004</v>
       </c>
-      <c r="L24" s="26">
+      <c r="L24" s="8">
         <v>0.25322499999999998</v>
       </c>
     </row>
     <row r="25" spans="4:12" ht="28">
-      <c r="D25" s="12"/>
+      <c r="D25" s="18"/>
       <c r="E25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="8">
         <v>28.016695000000002</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="8">
         <v>12.093688999999999</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="8">
         <v>12.618517000000001</v>
       </c>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26">
+      <c r="I25" s="8"/>
+      <c r="J25" s="8">
         <v>0.12972600000000001</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="8">
         <v>9.1367999999999991E-2</v>
       </c>
-      <c r="L25" s="26">
+      <c r="L25" s="8">
         <v>5.4265000000000001E-2</v>
       </c>
     </row>
     <row r="26" spans="4:12">
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="16" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="7">
         <v>329.88026099999996</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="7">
         <v>299.46396699999997</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="7">
         <v>245.86355899999998</v>
       </c>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25">
+      <c r="I26" s="7"/>
+      <c r="J26" s="7">
         <v>1.4905000000000002E-2</v>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="7">
         <v>2.9037299999999999</v>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="7">
         <v>2.3378380000000001</v>
       </c>
     </row>
     <row r="27" spans="4:12">
-      <c r="D27" s="11"/>
+      <c r="D27" s="17"/>
       <c r="E27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="7">
         <v>246.213842</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="7">
         <v>212.80277799999999</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="7">
         <v>179.01947200000001</v>
       </c>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25">
+      <c r="I27" s="7"/>
+      <c r="J27" s="7">
         <v>1.4905000000000002E-2</v>
       </c>
-      <c r="K27" s="25">
+      <c r="K27" s="7">
         <v>2.9037299999999999</v>
       </c>
-      <c r="L27" s="25">
+      <c r="L27" s="7">
         <v>0.61183799999999999</v>
       </c>
     </row>
     <row r="28" spans="4:12" ht="28">
-      <c r="D28" s="11"/>
+      <c r="D28" s="17"/>
       <c r="E28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F28" s="8">
         <v>88.131763000000007</v>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="8">
         <v>34.328474</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="8">
         <v>27.669065999999997</v>
       </c>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26">
-        <v>0</v>
-      </c>
-      <c r="K28" s="26">
-        <v>0</v>
-      </c>
-      <c r="L28" s="26">
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="4:12">
-      <c r="D29" s="11"/>
+      <c r="D29" s="17"/>
       <c r="E29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="8">
         <v>48.687129999999996</v>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="8">
         <v>73.112064000000004</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="8">
         <v>51.293977000000005</v>
       </c>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26">
-        <v>0</v>
-      </c>
-      <c r="K29" s="26">
-        <v>0</v>
-      </c>
-      <c r="L29" s="26">
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="4:12">
-      <c r="D30" s="11"/>
+      <c r="D30" s="17"/>
       <c r="E30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="8">
         <v>18.458897</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="8">
         <v>15.700310999999999</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="8">
         <v>16.349516000000001</v>
       </c>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26">
-        <v>0</v>
-      </c>
-      <c r="K30" s="26">
+      <c r="I30" s="8"/>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
         <v>0.75113399999999997</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="8">
         <v>0.12232999999999999</v>
       </c>
     </row>
     <row r="31" spans="4:12">
-      <c r="D31" s="11"/>
+      <c r="D31" s="17"/>
       <c r="E31" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="26">
-        <v>0</v>
-      </c>
-      <c r="G31" s="26">
-        <v>0</v>
-      </c>
-      <c r="H31" s="26">
-        <v>0</v>
-      </c>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26">
-        <v>0</v>
-      </c>
-      <c r="K31" s="26">
-        <v>0</v>
-      </c>
-      <c r="L31" s="26">
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="4:12">
-      <c r="D32" s="11"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="8">
         <v>0.72428999999999999</v>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="8">
         <v>2.1184220000000002</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="8">
         <v>1.0800299999999998</v>
       </c>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26">
-        <v>0</v>
-      </c>
-      <c r="K32" s="26">
+      <c r="I32" s="8"/>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
         <v>0.20630399999999999</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="8">
         <v>2.9700000000000001E-4</v>
       </c>
     </row>
     <row r="33" spans="4:12">
-      <c r="D33" s="11"/>
+      <c r="D33" s="17"/>
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="8">
         <v>0.53677399999999997</v>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="8">
         <v>0.58108000000000004</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="8">
         <v>0.63587700000000003</v>
       </c>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26">
+      <c r="I33" s="8"/>
+      <c r="J33" s="8">
         <v>5.6840000000000007E-3</v>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="8">
         <v>6.5290000000000009E-3</v>
       </c>
-      <c r="L33" s="26">
+      <c r="L33" s="8">
         <v>7.3680000000000004E-3</v>
       </c>
     </row>
     <row r="34" spans="4:12">
-      <c r="D34" s="11"/>
+      <c r="D34" s="17"/>
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="8">
         <v>15.877213000000001</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="8">
         <v>18.629577999999999</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="8">
         <v>16.727848000000002</v>
       </c>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26">
+      <c r="I34" s="8"/>
+      <c r="J34" s="8">
         <v>6.0169999999999998E-3</v>
       </c>
-      <c r="K34" s="26">
+      <c r="K34" s="8">
         <v>3.2726999999999999E-2</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="8">
         <v>2.1111999999999999E-2</v>
       </c>
     </row>
     <row r="35" spans="4:12">
-      <c r="D35" s="11"/>
+      <c r="D35" s="17"/>
       <c r="E35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="8">
         <v>18.185935000000001</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="8">
         <v>23.6157</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="8">
         <v>11.560713</v>
       </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26">
+      <c r="I35" s="8"/>
+      <c r="J35" s="8">
         <v>3.2049999999999995E-3</v>
       </c>
-      <c r="K35" s="26">
+      <c r="K35" s="8">
         <v>1.8716299999999999</v>
       </c>
-      <c r="L35" s="26">
+      <c r="L35" s="8">
         <v>3.9700000000000004E-3</v>
       </c>
     </row>
     <row r="36" spans="4:12">
-      <c r="D36" s="11"/>
+      <c r="D36" s="17"/>
       <c r="E36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="8">
         <v>6.8020990000000001</v>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="8">
         <v>3.3166389999999999</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="8">
         <v>12.728207000000001</v>
       </c>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26">
-        <v>0</v>
-      </c>
-      <c r="K36" s="26">
+      <c r="I36" s="8"/>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
         <v>3.5407000000000001E-2</v>
       </c>
-      <c r="L36" s="26">
+      <c r="L36" s="8">
         <v>0.38869300000000001</v>
       </c>
     </row>
     <row r="37" spans="4:12" ht="28">
-      <c r="D37" s="11"/>
+      <c r="D37" s="17"/>
       <c r="E37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="26">
+      <c r="F37" s="8">
         <v>48.809739</v>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="8">
         <v>41.400509999999997</v>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="8">
         <v>40.974237000000002</v>
       </c>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26">
-        <v>0</v>
-      </c>
-      <c r="K37" s="26">
-        <v>0</v>
-      </c>
-      <c r="L37" s="26">
+      <c r="I37" s="8"/>
+      <c r="J37" s="8">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8">
         <v>6.806799999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="4:12">
-      <c r="D38" s="11"/>
+      <c r="D38" s="17"/>
       <c r="E38" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="7">
         <v>83.666418999999991</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="7">
         <v>86.661189000000007</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="7">
         <v>66.844087000000002</v>
       </c>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25">
-        <v>0</v>
-      </c>
-      <c r="K38" s="25">
-        <v>0</v>
-      </c>
-      <c r="L38" s="25">
+      <c r="I38" s="7"/>
+      <c r="J38" s="7">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7">
+        <v>0</v>
+      </c>
+      <c r="L38" s="7">
         <v>1.726</v>
       </c>
     </row>
     <row r="39" spans="4:12" ht="28">
-      <c r="D39" s="11"/>
+      <c r="D39" s="17"/>
       <c r="E39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="8">
         <v>70.205049000000002</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="8">
         <v>76.681697</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="8">
         <v>60.783073999999999</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26">
-        <v>0</v>
-      </c>
-      <c r="K39" s="26">
-        <v>0</v>
-      </c>
-      <c r="L39" s="26">
+      <c r="I39" s="8"/>
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
         <v>1.726</v>
       </c>
     </row>
     <row r="40" spans="4:12">
-      <c r="D40" s="11"/>
+      <c r="D40" s="17"/>
       <c r="E40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="8">
         <v>2.9989999999999999E-3</v>
       </c>
-      <c r="G40" s="26">
+      <c r="G40" s="8">
         <v>5.9107000000000007E-2</v>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="8">
         <v>1.8671E-2</v>
       </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26">
-        <v>0</v>
-      </c>
-      <c r="K40" s="26">
-        <v>0</v>
-      </c>
-      <c r="L40" s="26">
+      <c r="I40" s="8"/>
+      <c r="J40" s="8">
+        <v>0</v>
+      </c>
+      <c r="K40" s="8">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="4:12">
-      <c r="D41" s="11"/>
+      <c r="D41" s="17"/>
       <c r="E41" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="26">
+      <c r="F41" s="8">
         <v>8.1160429999999995</v>
       </c>
-      <c r="G41" s="26">
+      <c r="G41" s="8">
         <v>3.9338900000000003</v>
       </c>
-      <c r="H41" s="26">
+      <c r="H41" s="8">
         <v>0.45526000000000005</v>
       </c>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26">
-        <v>0</v>
-      </c>
-      <c r="K41" s="26">
-        <v>0</v>
-      </c>
-      <c r="L41" s="26">
+      <c r="I41" s="8"/>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="4:12">
-      <c r="D42" s="11"/>
+      <c r="D42" s="17"/>
       <c r="E42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="26">
-        <v>0</v>
-      </c>
-      <c r="G42" s="26">
-        <v>0</v>
-      </c>
-      <c r="H42" s="26">
-        <v>0</v>
-      </c>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26">
-        <v>0</v>
-      </c>
-      <c r="K42" s="26">
-        <v>0</v>
-      </c>
-      <c r="L42" s="26">
+      <c r="F42" s="8">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8">
+        <v>0</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="4:12" ht="28">
-      <c r="D43" s="11"/>
+      <c r="D43" s="17"/>
       <c r="E43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="8">
         <v>0.85995300000000008</v>
       </c>
-      <c r="G43" s="26">
+      <c r="G43" s="8">
         <v>0.87562099999999987</v>
       </c>
-      <c r="H43" s="26">
+      <c r="H43" s="8">
         <v>0.67028299999999996</v>
       </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26">
-        <v>0</v>
-      </c>
-      <c r="K43" s="26">
-        <v>0</v>
-      </c>
-      <c r="L43" s="26">
+      <c r="I43" s="8"/>
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="4:12">
-      <c r="D44" s="12"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="8">
         <v>4.4823750000000002</v>
       </c>
-      <c r="G44" s="26">
+      <c r="G44" s="8">
         <v>5.1108739999999999</v>
       </c>
-      <c r="H44" s="26">
+      <c r="H44" s="8">
         <v>4.9168000000000003</v>
       </c>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26">
-        <v>0</v>
-      </c>
-      <c r="K44" s="26">
-        <v>0</v>
-      </c>
-      <c r="L44" s="26">
+      <c r="I44" s="8"/>
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="4:12">
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="19" t="s">
         <v>51</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="7">
         <v>241.08990699999998</v>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="7">
         <v>268.338953</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="7">
         <v>295.632743</v>
       </c>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25">
+      <c r="I45" s="7"/>
+      <c r="J45" s="7">
         <v>235.706592</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K45" s="7">
         <v>251.41704700000003</v>
       </c>
-      <c r="L45" s="25">
+      <c r="L45" s="7">
         <v>250.156092</v>
       </c>
     </row>
     <row r="46" spans="4:12" ht="28">
-      <c r="D46" s="14"/>
+      <c r="D46" s="20"/>
       <c r="E46" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="8">
         <v>46.518853999999997</v>
       </c>
-      <c r="G46" s="26">
+      <c r="G46" s="8">
         <v>46.518853999999997</v>
       </c>
-      <c r="H46" s="26">
+      <c r="H46" s="8">
         <v>46.287374</v>
       </c>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26">
+      <c r="I46" s="8"/>
+      <c r="J46" s="8">
         <v>46.518853999999997</v>
       </c>
-      <c r="K46" s="26">
+      <c r="K46" s="8">
         <v>46.518853999999997</v>
       </c>
-      <c r="L46" s="26">
+      <c r="L46" s="8">
         <v>46.287374</v>
       </c>
     </row>
     <row r="47" spans="4:12">
-      <c r="D47" s="14"/>
+      <c r="D47" s="20"/>
       <c r="E47" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="8">
         <v>88.258789000000007</v>
       </c>
-      <c r="G47" s="26">
+      <c r="G47" s="8">
         <v>88.258789000000007</v>
       </c>
-      <c r="H47" s="26">
+      <c r="H47" s="8">
         <v>86.990122</v>
       </c>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26">
+      <c r="I47" s="8"/>
+      <c r="J47" s="8">
         <v>161.90498500000001</v>
       </c>
-      <c r="K47" s="26">
+      <c r="K47" s="8">
         <v>161.90498500000001</v>
       </c>
-      <c r="L47" s="26">
+      <c r="L47" s="8">
         <v>160.63631699999999</v>
       </c>
     </row>
     <row r="48" spans="4:12">
-      <c r="D48" s="14"/>
+      <c r="D48" s="20"/>
       <c r="E48" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="26">
+      <c r="F48" s="8">
         <v>1.500148</v>
       </c>
-      <c r="G48" s="26">
+      <c r="G48" s="8">
         <v>2.500267</v>
       </c>
-      <c r="H48" s="26">
+      <c r="H48" s="8">
         <v>3.0003359999999999</v>
       </c>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26">
+      <c r="I48" s="8"/>
+      <c r="J48" s="8">
         <v>1.500148</v>
       </c>
-      <c r="K48" s="26">
+      <c r="K48" s="8">
         <v>2.500267</v>
       </c>
-      <c r="L48" s="26">
+      <c r="L48" s="8">
         <v>3.0003359999999999</v>
       </c>
     </row>
     <row r="49" spans="4:12">
-      <c r="D49" s="14"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="26">
+      <c r="F49" s="8">
         <v>-0.11168199999999999</v>
       </c>
-      <c r="G49" s="26">
+      <c r="G49" s="8">
         <v>-0.27036399999999999</v>
       </c>
-      <c r="H49" s="26">
+      <c r="H49" s="8">
         <v>-0.80546000000000006</v>
       </c>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26">
-        <v>0</v>
-      </c>
-      <c r="K49" s="26">
-        <v>0</v>
-      </c>
-      <c r="L49" s="26">
+      <c r="I49" s="8"/>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="4:12">
-      <c r="D50" s="14"/>
+      <c r="D50" s="20"/>
       <c r="E50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F50" s="26">
-        <v>0</v>
-      </c>
-      <c r="G50" s="26">
-        <v>0</v>
-      </c>
-      <c r="H50" s="26">
+      <c r="F50" s="8">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8">
         <v>0.11919300000000001</v>
       </c>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26">
+      <c r="I50" s="8"/>
+      <c r="J50" s="8">
         <v>4.8475999999999998E-2</v>
       </c>
-      <c r="K50" s="26">
+      <c r="K50" s="8">
         <v>4.8475999999999998E-2</v>
       </c>
-      <c r="L50" s="26">
+      <c r="L50" s="8">
         <v>4.8475999999999998E-2</v>
       </c>
     </row>
     <row r="51" spans="4:12">
-      <c r="D51" s="14"/>
+      <c r="D51" s="20"/>
       <c r="E51" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F51" s="26">
+      <c r="F51" s="8">
         <v>9.4044000000000008</v>
       </c>
-      <c r="G51" s="26">
+      <c r="G51" s="8">
         <v>12.690545</v>
       </c>
-      <c r="H51" s="26">
+      <c r="H51" s="8">
         <v>14.604691000000001</v>
       </c>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26">
+      <c r="I51" s="8"/>
+      <c r="J51" s="8">
         <v>5.7257249999999997</v>
       </c>
-      <c r="K51" s="26">
+      <c r="K51" s="8">
         <v>9.01187</v>
       </c>
-      <c r="L51" s="26">
+      <c r="L51" s="8">
         <v>10.926016000000001</v>
       </c>
     </row>
     <row r="52" spans="4:12">
-      <c r="D52" s="14"/>
+      <c r="D52" s="20"/>
       <c r="E52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="26">
+      <c r="F52" s="8">
         <v>98.499279000000001</v>
       </c>
-      <c r="G52" s="26">
+      <c r="G52" s="8">
         <v>123.616331</v>
       </c>
-      <c r="H52" s="26">
+      <c r="H52" s="8">
         <v>151.47846299999998</v>
       </c>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26">
+      <c r="I52" s="8"/>
+      <c r="J52" s="8">
         <v>23.008700000000001</v>
       </c>
-      <c r="K52" s="26">
+      <c r="K52" s="8">
         <v>36.433129000000001</v>
       </c>
-      <c r="L52" s="26">
+      <c r="L52" s="8">
         <v>35.258243999999998</v>
       </c>
     </row>
     <row r="53" spans="4:12">
-      <c r="D53" s="15"/>
+      <c r="D53" s="21"/>
       <c r="E53" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="26">
+      <c r="F53" s="8">
         <v>2.0413999999999998E-2</v>
       </c>
-      <c r="G53" s="26">
+      <c r="G53" s="8">
         <v>2.5063999999999999E-2</v>
       </c>
-      <c r="H53" s="26">
+      <c r="H53" s="8">
         <v>-4.1304E-2</v>
       </c>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26">
-        <v>0</v>
-      </c>
-      <c r="K53" s="26">
-        <v>0</v>
-      </c>
-      <c r="L53" s="26">
+      <c r="I53" s="8"/>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="4:12">
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="16" t="s">
         <v>61</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="26">
+      <c r="F54" s="8">
         <v>289.74772400000001</v>
       </c>
-      <c r="G54" s="26">
+      <c r="G54" s="8">
         <v>280.894273</v>
       </c>
-      <c r="H54" s="26">
+      <c r="H54" s="8">
         <v>295.02154900000005</v>
       </c>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26">
+      <c r="I54" s="8"/>
+      <c r="J54" s="8">
         <v>9.8123429999999985</v>
       </c>
-      <c r="K54" s="26">
+      <c r="K54" s="8">
         <v>71.641622999999996</v>
       </c>
-      <c r="L54" s="26">
+      <c r="L54" s="8">
         <v>1.467252</v>
       </c>
     </row>
     <row r="55" spans="4:12">
-      <c r="D55" s="11"/>
+      <c r="D55" s="17"/>
       <c r="E55" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="26">
+      <c r="F55" s="8">
         <v>248.89282200000002</v>
       </c>
-      <c r="G55" s="26">
+      <c r="G55" s="8">
         <v>215.538692</v>
       </c>
-      <c r="H55" s="26">
+      <c r="H55" s="8">
         <v>223.030879</v>
       </c>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26">
+      <c r="I55" s="8"/>
+      <c r="J55" s="8">
         <v>9.6832639999999994</v>
       </c>
-      <c r="K55" s="26">
+      <c r="K55" s="8">
         <v>70.262690000000006</v>
       </c>
-      <c r="L55" s="26">
+      <c r="L55" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="4:12" ht="28">
-      <c r="D56" s="11"/>
+      <c r="D56" s="17"/>
       <c r="E56" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F56" s="26">
+      <c r="F56" s="8">
         <v>4.6822339999999993</v>
       </c>
-      <c r="G56" s="26">
+      <c r="G56" s="8">
         <v>4.7361690000000003</v>
       </c>
-      <c r="H56" s="26">
+      <c r="H56" s="8">
         <v>5.5161940000000005</v>
       </c>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26">
+      <c r="I56" s="8"/>
+      <c r="J56" s="8">
         <v>5.4190999999999996E-2</v>
       </c>
-      <c r="K56" s="26">
+      <c r="K56" s="8">
         <v>6.2412999999999996E-2</v>
       </c>
-      <c r="L56" s="26">
+      <c r="L56" s="8">
         <v>7.5887999999999997E-2</v>
       </c>
     </row>
     <row r="57" spans="4:12">
-      <c r="D57" s="11"/>
+      <c r="D57" s="17"/>
       <c r="E57" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F57" s="26">
+      <c r="F57" s="8">
         <v>0.17657600000000001</v>
       </c>
-      <c r="G57" s="26">
+      <c r="G57" s="8">
         <v>0.18764600000000001</v>
       </c>
-      <c r="H57" s="26">
+      <c r="H57" s="8">
         <v>0.21928300000000001</v>
       </c>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26">
-        <v>0</v>
-      </c>
-      <c r="K57" s="26">
-        <v>0</v>
-      </c>
-      <c r="L57" s="26">
+      <c r="I57" s="8"/>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="4:12">
-      <c r="D58" s="11"/>
+      <c r="D58" s="17"/>
       <c r="E58" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F58" s="26">
+      <c r="F58" s="8">
         <v>3.4446029999999999</v>
       </c>
-      <c r="G58" s="26">
+      <c r="G58" s="8">
         <v>3.837825</v>
       </c>
-      <c r="H58" s="26">
+      <c r="H58" s="8">
         <v>4.45329</v>
       </c>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26">
+      <c r="I58" s="8"/>
+      <c r="J58" s="8">
         <v>0.90269599999999994</v>
       </c>
-      <c r="K58" s="26">
+      <c r="K58" s="8">
         <v>0.85908899999999999</v>
       </c>
-      <c r="L58" s="26">
+      <c r="L58" s="8">
         <v>0.93298799999999993</v>
       </c>
     </row>
     <row r="59" spans="4:12">
-      <c r="D59" s="11"/>
+      <c r="D59" s="17"/>
       <c r="E59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="26">
+      <c r="F59" s="8">
         <v>2.170598</v>
       </c>
-      <c r="G59" s="26">
+      <c r="G59" s="8">
         <v>2.1699919999999997</v>
       </c>
-      <c r="H59" s="26">
+      <c r="H59" s="8">
         <v>2.548047</v>
       </c>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26">
-        <v>0</v>
-      </c>
-      <c r="K59" s="26">
-        <v>0</v>
-      </c>
-      <c r="L59" s="26">
+      <c r="I59" s="8"/>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="4:12">
-      <c r="D60" s="11"/>
+      <c r="D60" s="17"/>
       <c r="E60" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F60" s="26">
+      <c r="F60" s="8">
         <v>7.8763619999999994</v>
       </c>
-      <c r="G60" s="26">
+      <c r="G60" s="8">
         <v>7.0695309999999996</v>
       </c>
-      <c r="H60" s="26">
+      <c r="H60" s="8">
         <v>4.6951739999999997</v>
       </c>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26">
+      <c r="I60" s="8"/>
+      <c r="J60" s="8">
         <v>7.5500000000000003E-4</v>
       </c>
-      <c r="K60" s="26">
+      <c r="K60" s="8">
         <v>0.10520999999999998</v>
       </c>
-      <c r="L60" s="26">
+      <c r="L60" s="8">
         <v>4.5123000000000003E-2</v>
       </c>
     </row>
     <row r="61" spans="4:12">
-      <c r="D61" s="11"/>
+      <c r="D61" s="17"/>
       <c r="E61" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F61" s="26">
+      <c r="F61" s="8">
         <v>3.887953</v>
       </c>
-      <c r="G61" s="26">
+      <c r="G61" s="8">
         <v>4.998024</v>
       </c>
-      <c r="H61" s="26">
+      <c r="H61" s="8">
         <v>2.7901500000000001</v>
       </c>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26">
+      <c r="I61" s="8"/>
+      <c r="J61" s="8">
         <v>1.0256999999999999E-2</v>
       </c>
-      <c r="K61" s="26">
+      <c r="K61" s="8">
         <v>5.3689999999999996E-3</v>
       </c>
-      <c r="L61" s="26">
+      <c r="L61" s="8">
         <v>2.2384999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="4:12">
-      <c r="D62" s="11"/>
+      <c r="D62" s="17"/>
       <c r="E62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F62" s="26">
-        <v>0</v>
-      </c>
-      <c r="G62" s="26">
-        <v>0</v>
-      </c>
-      <c r="H62" s="26">
-        <v>0</v>
-      </c>
-      <c r="I62" s="26"/>
-      <c r="J62" s="26">
+      <c r="F62" s="8">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="8">
+        <v>0</v>
+      </c>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8">
         <v>22</v>
       </c>
-      <c r="K62" s="26">
+      <c r="K62" s="8">
         <v>32.6</v>
       </c>
-      <c r="L62" s="26">
+      <c r="L62" s="8">
         <v>18.822443</v>
       </c>
     </row>
     <row r="63" spans="4:12" ht="42">
-      <c r="D63" s="11"/>
+      <c r="D63" s="17"/>
       <c r="E63" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F63" s="26">
-        <v>0</v>
-      </c>
-      <c r="G63" s="26">
-        <v>0</v>
-      </c>
-      <c r="H63" s="26">
-        <v>0</v>
-      </c>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26">
-        <v>0</v>
-      </c>
-      <c r="K63" s="26">
-        <v>0</v>
-      </c>
-      <c r="L63" s="26">
+      <c r="F63" s="8">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="8">
+        <v>0</v>
+      </c>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="4:12">
-      <c r="D64" s="11"/>
+      <c r="D64" s="17"/>
       <c r="E64" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F64" s="26">
+      <c r="F64" s="8">
         <v>2.8822000000000004E-2</v>
       </c>
-      <c r="G64" s="26">
+      <c r="G64" s="8">
         <v>-7.8436000000000006E-2</v>
       </c>
-      <c r="H64" s="26">
+      <c r="H64" s="8">
         <v>-0.204596</v>
       </c>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26">
+      <c r="I64" s="8"/>
+      <c r="J64" s="8">
         <v>9.4999999999999992E-5</v>
       </c>
-      <c r="K64" s="26">
+      <c r="K64" s="8">
         <v>-9.9999999999999995E-7</v>
       </c>
-      <c r="L64" s="26">
+      <c r="L64" s="8">
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="65" spans="4:12">
-      <c r="D65" s="11"/>
+      <c r="D65" s="17"/>
       <c r="E65" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F65" s="26">
+      <c r="F65" s="8">
         <v>-4.2110000000000003E-3</v>
       </c>
-      <c r="G65" s="26">
-        <v>0</v>
-      </c>
-      <c r="H65" s="26">
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="8">
         <v>-1.193981</v>
       </c>
-      <c r="I65" s="26"/>
-      <c r="J65" s="26">
-        <v>0</v>
-      </c>
-      <c r="K65" s="26">
-        <v>0</v>
-      </c>
-      <c r="L65" s="26">
+      <c r="I65" s="8"/>
+      <c r="J65" s="8">
+        <v>0</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="4:12">
-      <c r="D66" s="11"/>
+      <c r="D66" s="17"/>
       <c r="E66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="26">
-        <v>0</v>
-      </c>
-      <c r="G66" s="26">
+      <c r="F66" s="8">
+        <v>0</v>
+      </c>
+      <c r="G66" s="8">
         <v>-8.1986000000000003E-2</v>
       </c>
-      <c r="H66" s="26">
+      <c r="H66" s="8">
         <v>-1.2606000000000001E-2</v>
       </c>
-      <c r="I66" s="26"/>
-      <c r="J66" s="26">
-        <v>0</v>
-      </c>
-      <c r="K66" s="26">
-        <v>0</v>
-      </c>
-      <c r="L66" s="26">
+      <c r="I66" s="8"/>
+      <c r="J66" s="8">
+        <v>0</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="L66" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="4:12">
-      <c r="D67" s="11"/>
+      <c r="D67" s="17"/>
       <c r="E67" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F67" s="26">
+      <c r="F67" s="8">
         <v>0.16286900000000001</v>
       </c>
-      <c r="G67" s="26">
+      <c r="G67" s="8">
         <v>0.10903499999999999</v>
       </c>
-      <c r="H67" s="26">
+      <c r="H67" s="8">
         <v>8.6302000000000004E-2</v>
       </c>
-      <c r="I67" s="26"/>
-      <c r="J67" s="26">
+      <c r="I67" s="8"/>
+      <c r="J67" s="8">
         <v>2.4000000000000001E-5</v>
       </c>
-      <c r="K67" s="26">
-        <v>0</v>
-      </c>
-      <c r="L67" s="26">
+      <c r="K67" s="8">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="4:12">
-      <c r="D68" s="11"/>
+      <c r="D68" s="17"/>
       <c r="E68" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F68" s="26">
+      <c r="F68" s="8">
         <v>6.2226999999999998E-2</v>
       </c>
-      <c r="G68" s="26">
+      <c r="G68" s="8">
         <v>7.3797000000000001E-2</v>
       </c>
-      <c r="H68" s="26">
+      <c r="H68" s="8">
         <v>9.7528000000000004E-2</v>
       </c>
-      <c r="I68" s="26"/>
-      <c r="J68" s="26">
+      <c r="I68" s="8"/>
+      <c r="J68" s="8">
         <v>2.2205000000000003E-2</v>
       </c>
-      <c r="K68" s="26">
+      <c r="K68" s="8">
         <v>2E-3</v>
       </c>
-      <c r="L68" s="26">
+      <c r="L68" s="8">
         <v>2E-3</v>
       </c>
     </row>
     <row r="69" spans="4:12">
-      <c r="D69" s="11"/>
+      <c r="D69" s="17"/>
       <c r="E69" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F69" s="26">
+      <c r="F69" s="8">
         <v>26.517734000000001</v>
       </c>
-      <c r="G69" s="26">
+      <c r="G69" s="8">
         <v>52.227257999999999</v>
       </c>
-      <c r="H69" s="26">
+      <c r="H69" s="8">
         <v>55.926423</v>
       </c>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26">
+      <c r="I69" s="8"/>
+      <c r="J69" s="8">
         <v>21.159607999999999</v>
       </c>
-      <c r="K69" s="26">
+      <c r="K69" s="8">
         <v>32.955587999999999</v>
       </c>
-      <c r="L69" s="26">
+      <c r="L69" s="8">
         <v>19.256085000000002</v>
       </c>
     </row>
     <row r="70" spans="4:12">
-      <c r="D70" s="11"/>
+      <c r="D70" s="17"/>
       <c r="E70" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="8">
         <v>4.4626029999999997</v>
       </c>
-      <c r="G70" s="26">
+      <c r="G70" s="8">
         <v>7.6685369999999997</v>
       </c>
-      <c r="H70" s="26">
+      <c r="H70" s="8">
         <v>7.8141699999999998</v>
       </c>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26">
+      <c r="I70" s="8"/>
+      <c r="J70" s="8">
         <v>-0.18829699999999999</v>
       </c>
-      <c r="K70" s="26">
+      <c r="K70" s="8">
         <v>9.4133000000000008E-2</v>
       </c>
-      <c r="L70" s="26">
+      <c r="L70" s="8">
         <v>0.11462699999999999</v>
       </c>
     </row>
     <row r="71" spans="4:12">
-      <c r="D71" s="12"/>
+      <c r="D71" s="18"/>
       <c r="E71" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="7">
         <v>22.055130999999999</v>
       </c>
-      <c r="G71" s="25">
+      <c r="G71" s="7">
         <v>44.558721000000006</v>
       </c>
-      <c r="H71" s="25">
+      <c r="H71" s="7">
         <v>48.112253000000003</v>
       </c>
-      <c r="I71" s="25"/>
-      <c r="J71" s="25">
+      <c r="I71" s="7"/>
+      <c r="J71" s="7">
         <v>21.347904999999997</v>
       </c>
-      <c r="K71" s="25">
+      <c r="K71" s="7">
         <v>32.861454999999999</v>
       </c>
-      <c r="L71" s="25">
+      <c r="L71" s="7">
         <v>19.141458</v>
       </c>
     </row>
     <row r="72" spans="4:12" ht="42">
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="16" t="s">
         <v>80</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F72" s="26">
+      <c r="F72" s="8">
         <v>318.63</v>
       </c>
-      <c r="G72" s="26">
+      <c r="G72" s="8">
         <v>313.91000000000003</v>
       </c>
-      <c r="H72" s="26">
+      <c r="H72" s="8">
         <v>318.14</v>
       </c>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26">
+      <c r="I72" s="8"/>
+      <c r="J72" s="8">
         <v>11.09</v>
       </c>
-      <c r="K72" s="26">
+      <c r="K72" s="8">
         <v>80.37</v>
       </c>
-      <c r="L72" s="26">
+      <c r="L72" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="4:12" ht="28">
-      <c r="D73" s="11"/>
+      <c r="D73" s="17"/>
       <c r="E73" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F73" s="26">
+      <c r="F73" s="8">
         <v>39.163350999999999</v>
       </c>
-      <c r="G73" s="26">
+      <c r="G73" s="8">
         <v>52.201753000000004</v>
       </c>
-      <c r="H73" s="26">
+      <c r="H73" s="8">
         <v>80.52843</v>
       </c>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26">
+      <c r="I73" s="8"/>
+      <c r="J73" s="8">
         <v>-3.9457720000000003</v>
       </c>
-      <c r="K73" s="26">
+      <c r="K73" s="8">
         <v>-15.284420000000001</v>
       </c>
-      <c r="L73" s="26">
+      <c r="L73" s="8">
         <v>0.45628400000000002</v>
       </c>
     </row>
     <row r="74" spans="4:12" ht="28">
-      <c r="D74" s="11"/>
+      <c r="D74" s="17"/>
       <c r="E74" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F74" s="26">
+      <c r="F74" s="8">
         <v>-37.376781000000001</v>
       </c>
-      <c r="G74" s="26">
+      <c r="G74" s="8">
         <v>-21.157933</v>
       </c>
-      <c r="H74" s="26">
+      <c r="H74" s="8">
         <v>-15.863934</v>
       </c>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26">
+      <c r="I74" s="8"/>
+      <c r="J74" s="8">
         <v>13.248953</v>
       </c>
-      <c r="K74" s="26">
+      <c r="K74" s="8">
         <v>32.589048999999996</v>
       </c>
-      <c r="L74" s="26">
+      <c r="L74" s="8">
         <v>18.821306</v>
       </c>
     </row>
     <row r="75" spans="4:12" ht="28">
-      <c r="D75" s="11"/>
+      <c r="D75" s="17"/>
       <c r="E75" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F75" s="26">
+      <c r="F75" s="8">
         <v>1.00274</v>
       </c>
-      <c r="G75" s="26">
+      <c r="G75" s="8">
         <v>-35.759923999999998</v>
       </c>
-      <c r="H75" s="26">
+      <c r="H75" s="8">
         <v>-64.492998999999998</v>
       </c>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26">
+      <c r="I75" s="8"/>
+      <c r="J75" s="8">
         <v>-9.2973710000000001</v>
       </c>
-      <c r="K75" s="26">
+      <c r="K75" s="8">
         <v>-17.265646</v>
       </c>
-      <c r="L75" s="26">
+      <c r="L75" s="8">
         <v>-18.653129</v>
       </c>
     </row>
     <row r="76" spans="4:12">
-      <c r="D76" s="12"/>
+      <c r="D76" s="18"/>
       <c r="E76" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F76" s="25">
+      <c r="F76" s="7">
         <v>18.811067999999999</v>
       </c>
-      <c r="G76" s="25">
+      <c r="G76" s="7">
         <v>14.080121999999999</v>
       </c>
-      <c r="H76" s="25">
+      <c r="H76" s="7">
         <v>14.21599</v>
       </c>
-      <c r="I76" s="25"/>
-      <c r="J76" s="25">
+      <c r="I76" s="7"/>
+      <c r="J76" s="7">
         <v>5.3400999999999997E-2</v>
       </c>
-      <c r="K76" s="25">
+      <c r="K76" s="7">
         <v>9.2383000000000007E-2</v>
       </c>
-      <c r="L76" s="25">
+      <c r="L76" s="7">
         <v>0.71684499999999995</v>
       </c>
     </row>
     <row r="77" spans="4:12">
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="16" t="s">
         <v>86</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F77" s="27">
+      <c r="F77" s="9">
         <v>0.57779999999999998</v>
       </c>
-      <c r="G77" s="27">
+      <c r="G77" s="9">
         <v>0.52739999999999998</v>
       </c>
-      <c r="H77" s="27">
+      <c r="H77" s="9">
         <v>0.45400000000000001</v>
       </c>
-      <c r="I77" s="27"/>
-      <c r="J77" s="27">
+      <c r="I77" s="9"/>
+      <c r="J77" s="9">
         <v>1E-4</v>
       </c>
-      <c r="K77" s="27">
+      <c r="K77" s="9">
         <v>1.14E-2</v>
       </c>
-      <c r="L77" s="27">
+      <c r="L77" s="9">
         <v>9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="78" spans="4:12">
-      <c r="D78" s="11"/>
+      <c r="D78" s="17"/>
       <c r="E78" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F78" s="28">
+      <c r="F78" s="10">
         <v>0.87</v>
       </c>
-      <c r="G78" s="28">
+      <c r="G78" s="10">
         <v>0.98</v>
       </c>
-      <c r="H78" s="28">
+      <c r="H78" s="10">
         <v>1</v>
       </c>
-      <c r="I78" s="29"/>
-      <c r="J78" s="28">
+      <c r="I78" s="11"/>
+      <c r="J78" s="10">
         <v>23.94</v>
       </c>
-      <c r="K78" s="28">
+      <c r="K78" s="10">
         <v>6.58</v>
       </c>
-      <c r="L78" s="28">
+      <c r="L78" s="10">
         <v>28.53</v>
       </c>
     </row>
     <row r="79" spans="4:12">
-      <c r="D79" s="11"/>
+      <c r="D79" s="17"/>
       <c r="E79" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F79" s="28">
+      <c r="F79" s="10">
         <v>0.38</v>
       </c>
-      <c r="G79" s="28">
+      <c r="G79" s="10">
         <v>0.48</v>
       </c>
-      <c r="H79" s="28">
+      <c r="H79" s="10">
         <v>0.51</v>
       </c>
-      <c r="I79" s="29"/>
-      <c r="J79" s="28">
+      <c r="I79" s="11"/>
+      <c r="J79" s="10">
         <v>22.4</v>
       </c>
-      <c r="K79" s="28">
+      <c r="K79" s="10">
         <v>5.64</v>
       </c>
-      <c r="L79" s="28">
+      <c r="L79" s="10">
         <v>28.47</v>
       </c>
     </row>
     <row r="80" spans="4:12" ht="28">
-      <c r="D80" s="11"/>
+      <c r="D80" s="17"/>
       <c r="E80" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F80" s="30">
+      <c r="F80" s="12">
         <f t="shared" ref="F80:G80" si="0">F54/AVERAGE(E7,F7)</f>
         <v>57.060260637957441</v>
       </c>
-      <c r="G80" s="30">
+      <c r="G80" s="12">
         <f t="shared" si="0"/>
         <v>70.358084112061746</v>
       </c>
-      <c r="H80" s="30">
+      <c r="H80" s="12">
         <f>H54/AVERAGE(G7,H7)</f>
         <v>77.235755919851911</v>
       </c>
-      <c r="I80" s="30"/>
-      <c r="J80" s="28">
-        <v>0</v>
-      </c>
-      <c r="K80" s="28">
+      <c r="I80" s="12"/>
+      <c r="J80" s="10">
+        <v>0</v>
+      </c>
+      <c r="K80" s="10">
         <v>1.98</v>
       </c>
-      <c r="L80" s="28">
+      <c r="L80" s="10">
         <v>281.56</v>
       </c>
     </row>
     <row r="81" spans="4:12">
-      <c r="D81" s="11"/>
+      <c r="D81" s="17"/>
       <c r="E81" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F81" s="30">
+      <c r="F81" s="12">
         <f t="shared" ref="F81:H81" si="1">F55/AVERAGE(E11,F11)</f>
         <v>2.6080365448326397</v>
       </c>
-      <c r="G81" s="30">
+      <c r="G81" s="12">
         <f t="shared" si="1"/>
         <v>2.3469910826047711</v>
       </c>
-      <c r="H81" s="30">
+      <c r="H81" s="12">
         <f t="shared" si="1"/>
         <v>2.7859254099048134</v>
       </c>
-      <c r="I81" s="30"/>
-      <c r="J81" s="28">
-        <v>0</v>
-      </c>
-      <c r="K81" s="28">
+      <c r="I81" s="12"/>
+      <c r="J81" s="10">
+        <v>0</v>
+      </c>
+      <c r="K81" s="10">
         <v>2.42</v>
       </c>
-      <c r="L81" s="28"/>
+      <c r="L81" s="10"/>
     </row>
     <row r="82" spans="4:12">
-      <c r="D82" s="11"/>
+      <c r="D82" s="17"/>
       <c r="E82" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F82" s="27">
+      <c r="F82" s="9">
         <v>7.6100000000000001E-2</v>
       </c>
-      <c r="G82" s="27">
+      <c r="G82" s="9">
         <v>0.15859999999999999</v>
       </c>
-      <c r="H82" s="27">
+      <c r="H82" s="9">
         <v>0.16309999999999999</v>
       </c>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27">
+      <c r="I82" s="9"/>
+      <c r="J82" s="9">
         <v>2.1756000000000002</v>
       </c>
-      <c r="K82" s="27">
+      <c r="K82" s="9">
         <v>0.4587</v>
       </c>
-      <c r="L82" s="27">
+      <c r="L82" s="9">
         <v>13.0458</v>
       </c>
     </row>
     <row r="83" spans="4:12">
-      <c r="D83" s="11"/>
+      <c r="D83" s="17"/>
       <c r="E83" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F83" s="27">
+      <c r="F83" s="9">
         <v>0.14099999999999999</v>
       </c>
-      <c r="G83" s="27">
+      <c r="G83" s="9">
         <v>0.23269999999999999</v>
       </c>
-      <c r="H83" s="27">
+      <c r="H83" s="9">
         <v>0.24399999999999999</v>
       </c>
-      <c r="I83" s="27"/>
-      <c r="J83" s="27">
+      <c r="I83" s="9"/>
+      <c r="J83" s="9">
         <v>1.32E-2</v>
       </c>
-      <c r="K83" s="27">
+      <c r="K83" s="9">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="L83" s="27">
+      <c r="L83" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="4:12">
-      <c r="D84" s="11"/>
+      <c r="D84" s="17"/>
       <c r="E84" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F84" s="30">
+      <c r="F84" s="12">
         <f>SUM(F28,F29,F37)/F54</f>
         <v>0.64065604877710791</v>
       </c>
-      <c r="G84" s="30">
+      <c r="G84" s="12">
         <f t="shared" ref="G84:L84" si="2">SUM(G28,G29,G37)/G54</f>
         <v>0.52988281466315268</v>
       </c>
-      <c r="H84" s="30">
+      <c r="H84" s="12">
         <f t="shared" si="2"/>
         <v>0.40653735432729349</v>
       </c>
-      <c r="I84" s="30"/>
-      <c r="J84" s="30">
+      <c r="I84" s="12"/>
+      <c r="J84" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K84" s="30">
+      <c r="K84" s="12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L84" s="30">
+      <c r="L84" s="12">
         <f t="shared" si="2"/>
         <v>4.6391485579845855E-2</v>
       </c>
     </row>
     <row r="85" spans="4:12">
-      <c r="D85" s="12"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F85" s="30">
+      <c r="F85" s="12">
         <f>F72/F54</f>
         <v>1.099680769192168</v>
       </c>
-      <c r="G85" s="30">
+      <c r="G85" s="12">
         <f t="shared" ref="G85:L85" si="3">G72/G54</f>
         <v>1.1175379143454449</v>
       </c>
-      <c r="H85" s="30">
+      <c r="H85" s="12">
         <f t="shared" si="3"/>
         <v>1.0783619063704393</v>
       </c>
-      <c r="I85" s="30"/>
-      <c r="J85" s="30">
+      <c r="I85" s="12"/>
+      <c r="J85" s="12">
         <f t="shared" si="3"/>
         <v>1.1302091661492064</v>
       </c>
-      <c r="K85" s="30">
+      <c r="K85" s="12">
         <f t="shared" si="3"/>
         <v>1.1218338814015982</v>
       </c>
-      <c r="L85" s="30">
+      <c r="L85" s="12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="D54:D71"/>
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D85"/>
     <mergeCell ref="D1:E2"/>
@@ -3120,6 +3189,7 @@
     <mergeCell ref="D3:D25"/>
     <mergeCell ref="D26:D44"/>
     <mergeCell ref="D45:D53"/>
+    <mergeCell ref="D54:D71"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3132,10 +3202,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="4:9">
-      <c r="D1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="21"/>
+      <c r="D1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="27"/>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3150,7 +3220,7 @@
       </c>
     </row>
     <row r="2" spans="4:9">
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -3162,7 +3232,7 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="4:9">
-      <c r="D3" s="23"/>
+      <c r="D3" s="29"/>
       <c r="E3" s="2" t="s">
         <v>79</v>
       </c>
@@ -3172,7 +3242,7 @@
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="4:9">
-      <c r="D4" s="23"/>
+      <c r="D4" s="29"/>
       <c r="E4" s="2" t="s">
         <v>93</v>
       </c>
@@ -3182,7 +3252,7 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="4:9">
-      <c r="D5" s="24"/>
+      <c r="D5" s="30"/>
       <c r="E5" s="2" t="s">
         <v>92</v>
       </c>
@@ -3192,7 +3262,7 @@
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="4:9">
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -3204,7 +3274,7 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="4:9">
-      <c r="D7" s="23"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3214,7 +3284,7 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="4:9">
-      <c r="D8" s="23"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
@@ -3224,7 +3294,7 @@
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="4:9">
-      <c r="D9" s="23"/>
+      <c r="D9" s="29"/>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
@@ -3234,7 +3304,7 @@
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="4:9">
-      <c r="D10" s="23"/>
+      <c r="D10" s="29"/>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3244,7 +3314,7 @@
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="4:9">
-      <c r="D11" s="23"/>
+      <c r="D11" s="29"/>
       <c r="E11" s="2" t="s">
         <v>23</v>
       </c>
@@ -3254,7 +3324,7 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="4:9">
-      <c r="D12" s="23"/>
+      <c r="D12" s="29"/>
       <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
@@ -3264,7 +3334,7 @@
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="4:9">
-      <c r="D13" s="23"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="2" t="s">
         <v>99</v>
       </c>
@@ -3274,7 +3344,7 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="4:9" ht="28">
-      <c r="D14" s="23"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
@@ -3284,7 +3354,7 @@
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="4:9">
-      <c r="D15" s="23"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="2" t="s">
         <v>36</v>
       </c>
@@ -3294,7 +3364,7 @@
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="4:9">
-      <c r="D16" s="23"/>
+      <c r="D16" s="29"/>
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
@@ -3304,7 +3374,7 @@
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="4:9">
-      <c r="D17" s="23"/>
+      <c r="D17" s="29"/>
       <c r="E17" s="2" t="s">
         <v>52</v>
       </c>
@@ -3314,7 +3384,7 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="4:9">
-      <c r="D18" s="23"/>
+      <c r="D18" s="29"/>
       <c r="E18" s="2" t="s">
         <v>87</v>
       </c>
@@ -3324,7 +3394,7 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="4:9" ht="28">
-      <c r="D19" s="23"/>
+      <c r="D19" s="29"/>
       <c r="E19" s="2" t="s">
         <v>101</v>
       </c>
@@ -3334,7 +3404,7 @@
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="4:9">
-      <c r="D20" s="24"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="2" t="s">
         <v>102</v>
       </c>
@@ -3344,7 +3414,7 @@
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="4:9" ht="28">
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="28" t="s">
         <v>103</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -3356,7 +3426,7 @@
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="4:9" ht="42">
-      <c r="D22" s="23"/>
+      <c r="D22" s="29"/>
       <c r="E22" s="2" t="s">
         <v>81</v>
       </c>
@@ -3366,7 +3436,7 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="4:9">
-      <c r="D23" s="24"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="2" t="s">
         <v>95</v>
       </c>
@@ -3385,4 +3455,207 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43521169-F013-3040-9ABC-4628A30D5BEC}">
+  <dimension ref="H14:P26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="14" spans="8:16">
+      <c r="H14" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+    </row>
+    <row r="15" spans="8:16">
+      <c r="H15" s="31"/>
+      <c r="I15" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="8:16">
+      <c r="H16" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+    </row>
+    <row r="17" spans="8:16">
+      <c r="H17" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+    </row>
+    <row r="18" spans="8:16" ht="28">
+      <c r="H18" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+    </row>
+    <row r="19" spans="8:16" ht="28">
+      <c r="H19" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+    </row>
+    <row r="20" spans="8:16">
+      <c r="H20" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+    </row>
+    <row r="21" spans="8:16" ht="28">
+      <c r="H21" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+    </row>
+    <row r="22" spans="8:16">
+      <c r="H22" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+    </row>
+    <row r="23" spans="8:16">
+      <c r="H23" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+    </row>
+    <row r="24" spans="8:16">
+      <c r="H24" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+    </row>
+    <row r="25" spans="8:16">
+      <c r="H25" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+    </row>
+    <row r="26" spans="8:16">
+      <c r="H26" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="M14:P14"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial-report-excel-filler/references/财报填充.xlsx
+++ b/financial-report-excel-filler/references/财报填充.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c0f1953a9d5ec61e/文档/financial_report/financial-report-excel-filler/references/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyjie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{45FF6260-C262-A04A-A444-05C7F88DB74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7600FB-D57E-A64A-AC46-6FEF63E11B4A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FF6260-C262-A04A-A444-05C7F88DB74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="财报及财务指标" sheetId="1" r:id="rId1"/>
     <sheet name="简版财报（使用财务及财务指标sheet里的合并口径数据填充）" sheetId="2" r:id="rId2"/>
-    <sheet name="偿债分析（使用财报及财务指标sheet里的数据填充）" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="104">
   <si>
     <t>科目</t>
   </si>
@@ -347,38 +346,6 @@
   </si>
   <si>
     <t>现金流量</t>
-  </si>
-  <si>
-    <t>合并口径</t>
-  </si>
-  <si>
-    <t>单体口径</t>
-  </si>
-  <si>
-    <t>短期借款</t>
-  </si>
-  <si>
-    <t>短期刚性负债合计</t>
-  </si>
-  <si>
-    <t>长期借款</t>
-  </si>
-  <si>
-    <t>长期刚性负债合计</t>
-  </si>
-  <si>
-    <t>刚性负债合计</t>
-  </si>
-  <si>
-    <t>现金短债比</t>
-  </si>
-  <si>
-    <t>2023年</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>即期</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -386,10 +353,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -418,21 +385,6 @@
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -617,7 +569,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -627,34 +579,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -711,23 +645,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,10 +678,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1035,25 +965,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12">
-      <c r="D1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="13" t="s">
+      <c r="D1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="17"/>
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="13" t="s">
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="15"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" spans="4:12">
-      <c r="D2" s="24"/>
-      <c r="E2" s="25"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
@@ -1077,2110 +1007,2111 @@
       </c>
     </row>
     <row r="3" spans="4:12">
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="25">
         <v>570.97016799999994</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="25">
         <v>567.80291999999997</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="25">
         <v>541.49630300000001</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25">
         <v>235.721498</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="25">
         <v>254.32077699999999</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="25">
         <v>252.49392900000001</v>
       </c>
     </row>
     <row r="4" spans="4:12">
-      <c r="D4" s="17"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="25">
         <v>215.11788399999998</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="25">
         <v>209.31363200000001</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="25">
         <v>178.64533299999999</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
         <v>0.35689899999999997</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="25">
         <v>19.105357999999999</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="25">
         <v>17.45804</v>
       </c>
     </row>
     <row r="5" spans="4:12">
-      <c r="D5" s="17"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="26">
         <v>78.115516</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="26">
         <v>91.077581000000009</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="26">
         <v>65.397556000000009</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8">
+      <c r="I5" s="26"/>
+      <c r="J5" s="26">
         <v>5.3400999999999997E-2</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="26">
         <v>9.2383000000000007E-2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="26">
         <v>0.71684499999999995</v>
       </c>
     </row>
     <row r="6" spans="4:12">
-      <c r="D6" s="17"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="26">
         <v>9.9719750000000005</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="26">
         <v>6.0785349999999996</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="26">
         <v>17.670655</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
+      <c r="I6" s="26"/>
+      <c r="J6" s="26">
+        <v>0</v>
+      </c>
+      <c r="K6" s="26">
         <v>3.8587000000000003E-2</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="26">
         <v>0.388654</v>
       </c>
     </row>
     <row r="7" spans="4:12">
-      <c r="D7" s="17"/>
+      <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="26">
         <v>5.0779249999999996</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="26">
         <v>2.9067799999999999</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="26">
         <v>4.7327269999999997</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
+      <c r="I7" s="26"/>
+      <c r="J7" s="26">
+        <v>0</v>
+      </c>
+      <c r="K7" s="26">
         <v>0.78757100000000002</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="26">
         <v>1.5075700000000001</v>
       </c>
     </row>
     <row r="8" spans="4:12">
-      <c r="D8" s="17"/>
+      <c r="D8" s="11"/>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="26">
         <v>0.57736799999999999</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="26">
         <v>0.66803599999999996</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="26">
         <v>1.1283700000000001</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
+      <c r="I8" s="26"/>
+      <c r="J8" s="26">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="4:12">
-      <c r="D9" s="17"/>
+      <c r="D9" s="11"/>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="26">
         <v>20.780946</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="26">
         <v>15.084623000000001</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="26">
         <v>11.601576</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
+      <c r="I9" s="26"/>
+      <c r="J9" s="26">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26">
         <v>1.7559880000000001</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="26">
         <v>3.2490000000000002E-3</v>
       </c>
     </row>
     <row r="10" spans="4:12">
-      <c r="D10" s="17"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="26">
         <v>0.96690699999999996</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="26">
         <v>1.257773</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="26">
         <v>1.944834</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8">
+      <c r="I10" s="26"/>
+      <c r="J10" s="26">
         <v>0.28043400000000002</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="26">
         <v>15.456351999999999</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="26">
         <v>14.805128</v>
       </c>
     </row>
     <row r="11" spans="4:12">
-      <c r="D11" s="17"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="26">
         <v>95.433026999999996</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="26">
         <v>88.23933000000001</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="26">
         <v>71.873268999999993</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
+      <c r="I11" s="26"/>
+      <c r="J11" s="26">
+        <v>0</v>
+      </c>
+      <c r="K11" s="26">
         <v>0.94643700000000008</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="4:12" ht="28">
-      <c r="D12" s="17"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="26">
         <v>0.25</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="26">
         <v>0.375</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="26">
         <v>0.34499999999999997</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8">
-        <v>0</v>
-      </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8">
+      <c r="I12" s="26"/>
+      <c r="J12" s="26">
+        <v>0</v>
+      </c>
+      <c r="K12" s="26">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="4:12">
-      <c r="D13" s="17"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="26">
         <v>3.9442199999999996</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="26">
         <v>3.6259739999999998</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="26">
         <v>3.9513470000000002</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8">
+      <c r="I13" s="26"/>
+      <c r="J13" s="26">
         <v>2.3065000000000002E-2</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="26">
         <v>2.8039999999999999E-2</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="26">
         <v>3.6594000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="4:12">
-      <c r="D14" s="17"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="25">
         <v>355.852284</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="25">
         <v>358.48928899999999</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="25">
         <v>362.85096900000002</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7">
+      <c r="I14" s="25"/>
+      <c r="J14" s="25">
         <v>235.36459900000003</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="25">
         <v>235.215419</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="25">
         <v>235.03588999999999</v>
       </c>
     </row>
     <row r="15" spans="4:12" ht="28">
-      <c r="D15" s="17"/>
+      <c r="D15" s="11"/>
       <c r="E15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26">
+        <v>0</v>
+      </c>
+      <c r="K15" s="26">
+        <v>0</v>
+      </c>
+      <c r="L15" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="4:12" ht="28">
-      <c r="D16" s="17"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="8">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8">
+      <c r="F16" s="26">
+        <v>0</v>
+      </c>
+      <c r="G16" s="26">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26">
         <v>234.67099999999999</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="26">
         <v>234.67099999999999</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="26">
         <v>234.67099999999999</v>
       </c>
     </row>
     <row r="17" spans="4:12">
-      <c r="D17" s="17"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="26">
         <v>0.89600000000000002</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="26">
         <v>0.52100000000000002</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="26">
         <v>0.16</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
+      <c r="I17" s="26"/>
+      <c r="J17" s="26">
+        <v>0</v>
+      </c>
+      <c r="K17" s="26">
+        <v>0</v>
+      </c>
+      <c r="L17" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="4:12">
-      <c r="D18" s="17"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="26">
         <v>264.67085499999996</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="26">
         <v>273.507092</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="26">
         <v>286.74106499999999</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8">
+      <c r="I18" s="26"/>
+      <c r="J18" s="26">
         <v>9.6199000000000007E-2</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="26">
         <v>8.1419000000000005E-2</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="26">
         <v>5.5511999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="4:12">
-      <c r="D19" s="17"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="26">
         <v>43.442900999999999</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="26">
         <v>28.618996999999997</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="26">
         <v>18.770126000000001</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8">
+      <c r="I19" s="26"/>
+      <c r="J19" s="26">
+        <v>0</v>
+      </c>
+      <c r="K19" s="26">
+        <v>0</v>
+      </c>
+      <c r="L19" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="4:12">
-      <c r="D20" s="17"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="26">
         <v>1.4445E-2</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="26">
         <v>0.11541300000000002</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="26">
         <v>7.3358000000000007E-2</v>
       </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8">
-        <v>0</v>
-      </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8">
+      <c r="I20" s="26"/>
+      <c r="J20" s="26">
+        <v>0</v>
+      </c>
+      <c r="K20" s="26">
+        <v>0</v>
+      </c>
+      <c r="L20" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="4:12">
-      <c r="D21" s="17"/>
+      <c r="D21" s="11"/>
       <c r="E21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="8">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
+      <c r="F21" s="26">
+        <v>0</v>
+      </c>
+      <c r="G21" s="26">
+        <v>0</v>
+      </c>
+      <c r="H21" s="26">
+        <v>0</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26">
+        <v>0</v>
+      </c>
+      <c r="K21" s="26">
+        <v>0</v>
+      </c>
+      <c r="L21" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="4:12">
-      <c r="D22" s="17"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="26">
         <v>14.802370999999999</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="26">
         <v>38.363498</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="26">
         <v>38.383371000000004</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8">
+      <c r="I22" s="26"/>
+      <c r="J22" s="26">
         <v>5.6899999999999997E-3</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="26">
         <v>3.7810000000000001E-3</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="26">
         <v>1.8879999999999999E-3</v>
       </c>
     </row>
     <row r="23" spans="4:12">
-      <c r="D23" s="17"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="8">
-        <v>0</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8">
+      <c r="F23" s="26">
+        <v>0</v>
+      </c>
+      <c r="G23" s="26">
+        <v>0</v>
+      </c>
+      <c r="H23" s="26">
+        <v>0</v>
+      </c>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26">
+        <v>0</v>
+      </c>
+      <c r="K23" s="26">
+        <v>0</v>
+      </c>
+      <c r="L23" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="4:12" ht="28">
-      <c r="D24" s="17"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="26">
         <v>4.0090170000000001</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="26">
         <v>5.2695999999999996</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="26">
         <v>6.0426989999999998</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8">
+      <c r="I24" s="26"/>
+      <c r="J24" s="26">
         <v>0.46198400000000001</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="26">
         <v>0.36785100000000004</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="26">
         <v>0.25322499999999998</v>
       </c>
     </row>
     <row r="25" spans="4:12" ht="28">
-      <c r="D25" s="18"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="26">
         <v>28.016695000000002</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="26">
         <v>12.093688999999999</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="26">
         <v>12.618517000000001</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8">
+      <c r="I25" s="26"/>
+      <c r="J25" s="26">
         <v>0.12972600000000001</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="26">
         <v>9.1367999999999991E-2</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="26">
         <v>5.4265000000000001E-2</v>
       </c>
     </row>
     <row r="26" spans="4:12">
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="10" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="25">
         <v>329.88026099999996</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="25">
         <v>299.46396699999997</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="25">
         <v>245.86355899999998</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7">
+      <c r="I26" s="25"/>
+      <c r="J26" s="25">
         <v>1.4905000000000002E-2</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="25">
         <v>2.9037299999999999</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="25">
         <v>2.3378380000000001</v>
       </c>
     </row>
     <row r="27" spans="4:12">
-      <c r="D27" s="17"/>
+      <c r="D27" s="11"/>
       <c r="E27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="25">
         <v>246.213842</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="25">
         <v>212.80277799999999</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="25">
         <v>179.01947200000001</v>
       </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7">
+      <c r="I27" s="25"/>
+      <c r="J27" s="25">
         <v>1.4905000000000002E-2</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="25">
         <v>2.9037299999999999</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="25">
         <v>0.61183799999999999</v>
       </c>
     </row>
     <row r="28" spans="4:12" ht="28">
-      <c r="D28" s="17"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="26">
         <v>88.131763000000007</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="26">
         <v>34.328474</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="26">
         <v>27.669065999999997</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8">
-        <v>0</v>
-      </c>
-      <c r="K28" s="8">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8">
+      <c r="I28" s="26"/>
+      <c r="J28" s="26">
+        <v>0</v>
+      </c>
+      <c r="K28" s="26">
+        <v>0</v>
+      </c>
+      <c r="L28" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="4:12">
-      <c r="D29" s="17"/>
+      <c r="D29" s="11"/>
       <c r="E29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="26">
         <v>48.687129999999996</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="26">
         <v>73.112064000000004</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="26">
         <v>51.293977000000005</v>
       </c>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8">
-        <v>0</v>
-      </c>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8">
+      <c r="I29" s="26"/>
+      <c r="J29" s="26">
+        <v>0</v>
+      </c>
+      <c r="K29" s="26">
+        <v>0</v>
+      </c>
+      <c r="L29" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="4:12">
-      <c r="D30" s="17"/>
+      <c r="D30" s="11"/>
       <c r="E30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="26">
         <v>18.458897</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="26">
         <v>15.700310999999999</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="26">
         <v>16.349516000000001</v>
       </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8">
-        <v>0</v>
-      </c>
-      <c r="K30" s="8">
+      <c r="I30" s="26"/>
+      <c r="J30" s="26">
+        <v>0</v>
+      </c>
+      <c r="K30" s="26">
         <v>0.75113399999999997</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="26">
         <v>0.12232999999999999</v>
       </c>
     </row>
     <row r="31" spans="4:12">
-      <c r="D31" s="17"/>
+      <c r="D31" s="11"/>
       <c r="E31" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="8">
-        <v>0</v>
-      </c>
-      <c r="G31" s="8">
-        <v>0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8">
+      <c r="F31" s="26">
+        <v>0</v>
+      </c>
+      <c r="G31" s="26">
+        <v>0</v>
+      </c>
+      <c r="H31" s="26">
+        <v>0</v>
+      </c>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26">
+        <v>0</v>
+      </c>
+      <c r="K31" s="26">
+        <v>0</v>
+      </c>
+      <c r="L31" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="4:12">
-      <c r="D32" s="17"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="26">
         <v>0.72428999999999999</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="26">
         <v>2.1184220000000002</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="26">
         <v>1.0800299999999998</v>
       </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8">
-        <v>0</v>
-      </c>
-      <c r="K32" s="8">
+      <c r="I32" s="26"/>
+      <c r="J32" s="26">
+        <v>0</v>
+      </c>
+      <c r="K32" s="26">
         <v>0.20630399999999999</v>
       </c>
-      <c r="L32" s="8">
+      <c r="L32" s="26">
         <v>2.9700000000000001E-4</v>
       </c>
     </row>
     <row r="33" spans="4:12">
-      <c r="D33" s="17"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="26">
         <v>0.53677399999999997</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="26">
         <v>0.58108000000000004</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="26">
         <v>0.63587700000000003</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8">
+      <c r="I33" s="26"/>
+      <c r="J33" s="26">
         <v>5.6840000000000007E-3</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="26">
         <v>6.5290000000000009E-3</v>
       </c>
-      <c r="L33" s="8">
+      <c r="L33" s="26">
         <v>7.3680000000000004E-3</v>
       </c>
     </row>
     <row r="34" spans="4:12">
-      <c r="D34" s="17"/>
+      <c r="D34" s="11"/>
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="26">
         <v>15.877213000000001</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="26">
         <v>18.629577999999999</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="26">
         <v>16.727848000000002</v>
       </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8">
+      <c r="I34" s="26"/>
+      <c r="J34" s="26">
         <v>6.0169999999999998E-3</v>
       </c>
-      <c r="K34" s="8">
+      <c r="K34" s="26">
         <v>3.2726999999999999E-2</v>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="26">
         <v>2.1111999999999999E-2</v>
       </c>
     </row>
     <row r="35" spans="4:12">
-      <c r="D35" s="17"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="26">
         <v>18.185935000000001</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="26">
         <v>23.6157</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="26">
         <v>11.560713</v>
       </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8">
+      <c r="I35" s="26"/>
+      <c r="J35" s="26">
         <v>3.2049999999999995E-3</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="26">
         <v>1.8716299999999999</v>
       </c>
-      <c r="L35" s="8">
+      <c r="L35" s="26">
         <v>3.9700000000000004E-3</v>
       </c>
     </row>
     <row r="36" spans="4:12">
-      <c r="D36" s="17"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="26">
         <v>6.8020990000000001</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="26">
         <v>3.3166389999999999</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="26">
         <v>12.728207000000001</v>
       </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8">
-        <v>0</v>
-      </c>
-      <c r="K36" s="8">
+      <c r="I36" s="26"/>
+      <c r="J36" s="26">
+        <v>0</v>
+      </c>
+      <c r="K36" s="26">
         <v>3.5407000000000001E-2</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="26">
         <v>0.38869300000000001</v>
       </c>
     </row>
     <row r="37" spans="4:12" ht="28">
-      <c r="D37" s="17"/>
+      <c r="D37" s="11"/>
       <c r="E37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="26">
         <v>48.809739</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="26">
         <v>41.400509999999997</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="26">
         <v>40.974237000000002</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8">
-        <v>0</v>
-      </c>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8">
+      <c r="I37" s="26"/>
+      <c r="J37" s="26">
+        <v>0</v>
+      </c>
+      <c r="K37" s="26">
+        <v>0</v>
+      </c>
+      <c r="L37" s="26">
         <v>6.806799999999999E-2</v>
       </c>
     </row>
     <row r="38" spans="4:12">
-      <c r="D38" s="17"/>
+      <c r="D38" s="11"/>
       <c r="E38" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="25">
         <v>83.666418999999991</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="25">
         <v>86.661189000000007</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="25">
         <v>66.844087000000002</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7">
-        <v>0</v>
-      </c>
-      <c r="L38" s="7">
+      <c r="I38" s="25"/>
+      <c r="J38" s="25">
+        <v>0</v>
+      </c>
+      <c r="K38" s="25">
+        <v>0</v>
+      </c>
+      <c r="L38" s="25">
         <v>1.726</v>
       </c>
     </row>
     <row r="39" spans="4:12" ht="28">
-      <c r="D39" s="17"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="26">
         <v>70.205049000000002</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="26">
         <v>76.681697</v>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="26">
         <v>60.783073999999999</v>
       </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8">
-        <v>0</v>
-      </c>
-      <c r="K39" s="8">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8">
+      <c r="I39" s="26"/>
+      <c r="J39" s="26">
+        <v>0</v>
+      </c>
+      <c r="K39" s="26">
+        <v>0</v>
+      </c>
+      <c r="L39" s="26">
         <v>1.726</v>
       </c>
     </row>
     <row r="40" spans="4:12">
-      <c r="D40" s="17"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="26">
         <v>2.9989999999999999E-3</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="26">
         <v>5.9107000000000007E-2</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="26">
         <v>1.8671E-2</v>
       </c>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8">
-        <v>0</v>
-      </c>
-      <c r="K40" s="8">
-        <v>0</v>
-      </c>
-      <c r="L40" s="8">
+      <c r="I40" s="26"/>
+      <c r="J40" s="26">
+        <v>0</v>
+      </c>
+      <c r="K40" s="26">
+        <v>0</v>
+      </c>
+      <c r="L40" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="4:12">
-      <c r="D41" s="17"/>
+      <c r="D41" s="11"/>
       <c r="E41" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="26">
         <v>8.1160429999999995</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="26">
         <v>3.9338900000000003</v>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="26">
         <v>0.45526000000000005</v>
       </c>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8">
-        <v>0</v>
-      </c>
-      <c r="K41" s="8">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8">
+      <c r="I41" s="26"/>
+      <c r="J41" s="26">
+        <v>0</v>
+      </c>
+      <c r="K41" s="26">
+        <v>0</v>
+      </c>
+      <c r="L41" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="4:12">
-      <c r="D42" s="17"/>
+      <c r="D42" s="11"/>
       <c r="E42" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="8">
-        <v>0</v>
-      </c>
-      <c r="G42" s="8">
-        <v>0</v>
-      </c>
-      <c r="H42" s="8">
-        <v>0</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8">
-        <v>0</v>
-      </c>
-      <c r="K42" s="8">
-        <v>0</v>
-      </c>
-      <c r="L42" s="8">
+      <c r="F42" s="26">
+        <v>0</v>
+      </c>
+      <c r="G42" s="26">
+        <v>0</v>
+      </c>
+      <c r="H42" s="26">
+        <v>0</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26">
+        <v>0</v>
+      </c>
+      <c r="K42" s="26">
+        <v>0</v>
+      </c>
+      <c r="L42" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="4:12" ht="28">
-      <c r="D43" s="17"/>
+      <c r="D43" s="11"/>
       <c r="E43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="26">
         <v>0.85995300000000008</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="26">
         <v>0.87562099999999987</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="26">
         <v>0.67028299999999996</v>
       </c>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="8">
+      <c r="I43" s="26"/>
+      <c r="J43" s="26">
+        <v>0</v>
+      </c>
+      <c r="K43" s="26">
+        <v>0</v>
+      </c>
+      <c r="L43" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="4:12">
-      <c r="D44" s="18"/>
+      <c r="D44" s="12"/>
       <c r="E44" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="26">
         <v>4.4823750000000002</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="26">
         <v>5.1108739999999999</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="26">
         <v>4.9168000000000003</v>
       </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8">
-        <v>0</v>
-      </c>
-      <c r="K44" s="8">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8">
+      <c r="I44" s="26"/>
+      <c r="J44" s="26">
+        <v>0</v>
+      </c>
+      <c r="K44" s="26">
+        <v>0</v>
+      </c>
+      <c r="L44" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="4:12">
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="13" t="s">
         <v>51</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="25">
         <v>241.08990699999998</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="25">
         <v>268.338953</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="25">
         <v>295.632743</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7">
+      <c r="I45" s="25"/>
+      <c r="J45" s="25">
         <v>235.706592</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="25">
         <v>251.41704700000003</v>
       </c>
-      <c r="L45" s="7">
+      <c r="L45" s="25">
         <v>250.156092</v>
       </c>
     </row>
     <row r="46" spans="4:12" ht="28">
-      <c r="D46" s="20"/>
+      <c r="D46" s="14"/>
       <c r="E46" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="26">
         <v>46.518853999999997</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="26">
         <v>46.518853999999997</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="26">
         <v>46.287374</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8">
+      <c r="I46" s="26"/>
+      <c r="J46" s="26">
         <v>46.518853999999997</v>
       </c>
-      <c r="K46" s="8">
+      <c r="K46" s="26">
         <v>46.518853999999997</v>
       </c>
-      <c r="L46" s="8">
+      <c r="L46" s="26">
         <v>46.287374</v>
       </c>
     </row>
     <row r="47" spans="4:12">
-      <c r="D47" s="20"/>
+      <c r="D47" s="14"/>
       <c r="E47" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="26">
         <v>88.258789000000007</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="26">
         <v>88.258789000000007</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="26">
         <v>86.990122</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8">
+      <c r="I47" s="26"/>
+      <c r="J47" s="26">
         <v>161.90498500000001</v>
       </c>
-      <c r="K47" s="8">
+      <c r="K47" s="26">
         <v>161.90498500000001</v>
       </c>
-      <c r="L47" s="8">
+      <c r="L47" s="26">
         <v>160.63631699999999</v>
       </c>
     </row>
     <row r="48" spans="4:12">
-      <c r="D48" s="20"/>
+      <c r="D48" s="14"/>
       <c r="E48" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="26">
         <v>1.500148</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="26">
         <v>2.500267</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="26">
         <v>3.0003359999999999</v>
       </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8">
+      <c r="I48" s="26"/>
+      <c r="J48" s="26">
         <v>1.500148</v>
       </c>
-      <c r="K48" s="8">
+      <c r="K48" s="26">
         <v>2.500267</v>
       </c>
-      <c r="L48" s="8">
+      <c r="L48" s="26">
         <v>3.0003359999999999</v>
       </c>
     </row>
     <row r="49" spans="4:12">
-      <c r="D49" s="20"/>
+      <c r="D49" s="14"/>
       <c r="E49" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="26">
         <v>-0.11168199999999999</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="26">
         <v>-0.27036399999999999</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="26">
         <v>-0.80546000000000006</v>
       </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8">
-        <v>0</v>
-      </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8">
+      <c r="I49" s="26"/>
+      <c r="J49" s="26">
+        <v>0</v>
+      </c>
+      <c r="K49" s="26">
+        <v>0</v>
+      </c>
+      <c r="L49" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="4:12">
-      <c r="D50" s="20"/>
+      <c r="D50" s="14"/>
       <c r="E50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F50" s="8">
-        <v>0</v>
-      </c>
-      <c r="G50" s="8">
-        <v>0</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="F50" s="26">
+        <v>0</v>
+      </c>
+      <c r="G50" s="26">
+        <v>0</v>
+      </c>
+      <c r="H50" s="26">
         <v>0.11919300000000001</v>
       </c>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8">
+      <c r="I50" s="26"/>
+      <c r="J50" s="26">
         <v>4.8475999999999998E-2</v>
       </c>
-      <c r="K50" s="8">
+      <c r="K50" s="26">
         <v>4.8475999999999998E-2</v>
       </c>
-      <c r="L50" s="8">
+      <c r="L50" s="26">
         <v>4.8475999999999998E-2</v>
       </c>
     </row>
     <row r="51" spans="4:12">
-      <c r="D51" s="20"/>
+      <c r="D51" s="14"/>
       <c r="E51" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="26">
         <v>9.4044000000000008</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="26">
         <v>12.690545</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="26">
         <v>14.604691000000001</v>
       </c>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8">
+      <c r="I51" s="26"/>
+      <c r="J51" s="26">
         <v>5.7257249999999997</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="26">
         <v>9.01187</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="26">
         <v>10.926016000000001</v>
       </c>
     </row>
     <row r="52" spans="4:12">
-      <c r="D52" s="20"/>
+      <c r="D52" s="14"/>
       <c r="E52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="26">
         <v>98.499279000000001</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="26">
         <v>123.616331</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="26">
         <v>151.47846299999998</v>
       </c>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8">
+      <c r="I52" s="26"/>
+      <c r="J52" s="26">
         <v>23.008700000000001</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="26">
         <v>36.433129000000001</v>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="26">
         <v>35.258243999999998</v>
       </c>
     </row>
     <row r="53" spans="4:12">
-      <c r="D53" s="21"/>
+      <c r="D53" s="15"/>
       <c r="E53" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="26">
         <v>2.0413999999999998E-2</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="26">
         <v>2.5063999999999999E-2</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="26">
         <v>-4.1304E-2</v>
       </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8">
-        <v>0</v>
-      </c>
-      <c r="L53" s="8">
+      <c r="I53" s="26"/>
+      <c r="J53" s="26">
+        <v>0</v>
+      </c>
+      <c r="K53" s="26">
+        <v>0</v>
+      </c>
+      <c r="L53" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="4:12">
-      <c r="D54" s="16" t="s">
+      <c r="D54" s="10" t="s">
         <v>61</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="26">
         <v>289.74772400000001</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="26">
         <v>280.894273</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="26">
         <v>295.02154900000005</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8">
+      <c r="I54" s="26"/>
+      <c r="J54" s="26">
         <v>9.8123429999999985</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="26">
         <v>71.641622999999996</v>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="26">
         <v>1.467252</v>
       </c>
     </row>
     <row r="55" spans="4:12">
-      <c r="D55" s="17"/>
+      <c r="D55" s="11"/>
       <c r="E55" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="26">
         <v>248.89282200000002</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="26">
         <v>215.538692</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="26">
         <v>223.030879</v>
       </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8">
+      <c r="I55" s="26"/>
+      <c r="J55" s="26">
         <v>9.6832639999999994</v>
       </c>
-      <c r="K55" s="8">
+      <c r="K55" s="26">
         <v>70.262690000000006</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="4:12" ht="28">
-      <c r="D56" s="17"/>
+      <c r="D56" s="11"/>
       <c r="E56" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="26">
         <v>4.6822339999999993</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="26">
         <v>4.7361690000000003</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="26">
         <v>5.5161940000000005</v>
       </c>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8">
+      <c r="I56" s="26"/>
+      <c r="J56" s="26">
         <v>5.4190999999999996E-2</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K56" s="26">
         <v>6.2412999999999996E-2</v>
       </c>
-      <c r="L56" s="8">
+      <c r="L56" s="26">
         <v>7.5887999999999997E-2</v>
       </c>
     </row>
     <row r="57" spans="4:12">
-      <c r="D57" s="17"/>
+      <c r="D57" s="11"/>
       <c r="E57" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="26">
         <v>0.17657600000000001</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="26">
         <v>0.18764600000000001</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="26">
         <v>0.21928300000000001</v>
       </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8">
-        <v>0</v>
-      </c>
-      <c r="L57" s="8">
+      <c r="I57" s="26"/>
+      <c r="J57" s="26">
+        <v>0</v>
+      </c>
+      <c r="K57" s="26">
+        <v>0</v>
+      </c>
+      <c r="L57" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="4:12">
-      <c r="D58" s="17"/>
+      <c r="D58" s="11"/>
       <c r="E58" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="26">
         <v>3.4446029999999999</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="26">
         <v>3.837825</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="26">
         <v>4.45329</v>
       </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8">
+      <c r="I58" s="26"/>
+      <c r="J58" s="26">
         <v>0.90269599999999994</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="26">
         <v>0.85908899999999999</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="26">
         <v>0.93298799999999993</v>
       </c>
     </row>
     <row r="59" spans="4:12">
-      <c r="D59" s="17"/>
+      <c r="D59" s="11"/>
       <c r="E59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="26">
         <v>2.170598</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="26">
         <v>2.1699919999999997</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="26">
         <v>2.548047</v>
       </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8">
-        <v>0</v>
-      </c>
-      <c r="K59" s="8">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8">
+      <c r="I59" s="26"/>
+      <c r="J59" s="26">
+        <v>0</v>
+      </c>
+      <c r="K59" s="26">
+        <v>0</v>
+      </c>
+      <c r="L59" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="4:12">
-      <c r="D60" s="17"/>
+      <c r="D60" s="11"/>
       <c r="E60" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="26">
         <v>7.8763619999999994</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="26">
         <v>7.0695309999999996</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="26">
         <v>4.6951739999999997</v>
       </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8">
+      <c r="I60" s="26"/>
+      <c r="J60" s="26">
         <v>7.5500000000000003E-4</v>
       </c>
-      <c r="K60" s="8">
+      <c r="K60" s="26">
         <v>0.10520999999999998</v>
       </c>
-      <c r="L60" s="8">
+      <c r="L60" s="26">
         <v>4.5123000000000003E-2</v>
       </c>
     </row>
     <row r="61" spans="4:12">
-      <c r="D61" s="17"/>
+      <c r="D61" s="11"/>
       <c r="E61" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="26">
         <v>3.887953</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="26">
         <v>4.998024</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="26">
         <v>2.7901500000000001</v>
       </c>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8">
+      <c r="I61" s="26"/>
+      <c r="J61" s="26">
         <v>1.0256999999999999E-2</v>
       </c>
-      <c r="K61" s="8">
+      <c r="K61" s="26">
         <v>5.3689999999999996E-3</v>
       </c>
-      <c r="L61" s="8">
+      <c r="L61" s="26">
         <v>2.2384999999999999E-2</v>
       </c>
     </row>
     <row r="62" spans="4:12">
-      <c r="D62" s="17"/>
+      <c r="D62" s="11"/>
       <c r="E62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F62" s="8">
-        <v>0</v>
-      </c>
-      <c r="G62" s="8">
-        <v>0</v>
-      </c>
-      <c r="H62" s="8">
-        <v>0</v>
-      </c>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8">
+      <c r="F62" s="26">
+        <v>0</v>
+      </c>
+      <c r="G62" s="26">
+        <v>0</v>
+      </c>
+      <c r="H62" s="26">
+        <v>0</v>
+      </c>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26">
         <v>22</v>
       </c>
-      <c r="K62" s="8">
+      <c r="K62" s="26">
         <v>32.6</v>
       </c>
-      <c r="L62" s="8">
+      <c r="L62" s="26">
         <v>18.822443</v>
       </c>
     </row>
     <row r="63" spans="4:12" ht="42">
-      <c r="D63" s="17"/>
+      <c r="D63" s="11"/>
       <c r="E63" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F63" s="8">
-        <v>0</v>
-      </c>
-      <c r="G63" s="8">
-        <v>0</v>
-      </c>
-      <c r="H63" s="8">
-        <v>0</v>
-      </c>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
-      <c r="K63" s="8">
-        <v>0</v>
-      </c>
-      <c r="L63" s="8">
+      <c r="F63" s="26">
+        <v>0</v>
+      </c>
+      <c r="G63" s="26">
+        <v>0</v>
+      </c>
+      <c r="H63" s="26">
+        <v>0</v>
+      </c>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26">
+        <v>0</v>
+      </c>
+      <c r="K63" s="26">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="4:12">
-      <c r="D64" s="17"/>
+      <c r="D64" s="11"/>
       <c r="E64" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="26">
         <v>2.8822000000000004E-2</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="26">
         <v>-7.8436000000000006E-2</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="26">
         <v>-0.204596</v>
       </c>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8">
+      <c r="I64" s="26"/>
+      <c r="J64" s="26">
         <v>9.4999999999999992E-5</v>
       </c>
-      <c r="K64" s="8">
+      <c r="K64" s="26">
         <v>-9.9999999999999995E-7</v>
       </c>
-      <c r="L64" s="8">
+      <c r="L64" s="26">
         <v>5.0000000000000004E-6</v>
       </c>
     </row>
     <row r="65" spans="4:12">
-      <c r="D65" s="17"/>
+      <c r="D65" s="11"/>
       <c r="E65" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="26">
         <v>-4.2110000000000003E-3</v>
       </c>
-      <c r="G65" s="8">
-        <v>0</v>
-      </c>
-      <c r="H65" s="8">
+      <c r="G65" s="26">
+        <v>0</v>
+      </c>
+      <c r="H65" s="26">
         <v>-1.193981</v>
       </c>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8">
-        <v>0</v>
-      </c>
-      <c r="K65" s="8">
-        <v>0</v>
-      </c>
-      <c r="L65" s="8">
+      <c r="I65" s="26"/>
+      <c r="J65" s="26">
+        <v>0</v>
+      </c>
+      <c r="K65" s="26">
+        <v>0</v>
+      </c>
+      <c r="L65" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="4:12">
-      <c r="D66" s="17"/>
+      <c r="D66" s="11"/>
       <c r="E66" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F66" s="8">
-        <v>0</v>
-      </c>
-      <c r="G66" s="8">
+      <c r="F66" s="26">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26">
         <v>-8.1986000000000003E-2</v>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="26">
         <v>-1.2606000000000001E-2</v>
       </c>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8">
-        <v>0</v>
-      </c>
-      <c r="K66" s="8">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8">
+      <c r="I66" s="26"/>
+      <c r="J66" s="26">
+        <v>0</v>
+      </c>
+      <c r="K66" s="26">
+        <v>0</v>
+      </c>
+      <c r="L66" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="4:12">
-      <c r="D67" s="17"/>
+      <c r="D67" s="11"/>
       <c r="E67" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="26">
         <v>0.16286900000000001</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="26">
         <v>0.10903499999999999</v>
       </c>
-      <c r="H67" s="8">
+      <c r="H67" s="26">
         <v>8.6302000000000004E-2</v>
       </c>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8">
+      <c r="I67" s="26"/>
+      <c r="J67" s="26">
         <v>2.4000000000000001E-5</v>
       </c>
-      <c r="K67" s="8">
-        <v>0</v>
-      </c>
-      <c r="L67" s="8">
+      <c r="K67" s="26">
+        <v>0</v>
+      </c>
+      <c r="L67" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="4:12">
-      <c r="D68" s="17"/>
+      <c r="D68" s="11"/>
       <c r="E68" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="26">
         <v>6.2226999999999998E-2</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="26">
         <v>7.3797000000000001E-2</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="26">
         <v>9.7528000000000004E-2</v>
       </c>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8">
+      <c r="I68" s="26"/>
+      <c r="J68" s="26">
         <v>2.2205000000000003E-2</v>
       </c>
-      <c r="K68" s="8">
+      <c r="K68" s="26">
         <v>2E-3</v>
       </c>
-      <c r="L68" s="8">
+      <c r="L68" s="26">
         <v>2E-3</v>
       </c>
     </row>
     <row r="69" spans="4:12">
-      <c r="D69" s="17"/>
+      <c r="D69" s="11"/>
       <c r="E69" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="26">
         <v>26.517734000000001</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="26">
         <v>52.227257999999999</v>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="26">
         <v>55.926423</v>
       </c>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8">
+      <c r="I69" s="26"/>
+      <c r="J69" s="26">
         <v>21.159607999999999</v>
       </c>
-      <c r="K69" s="8">
+      <c r="K69" s="26">
         <v>32.955587999999999</v>
       </c>
-      <c r="L69" s="8">
+      <c r="L69" s="26">
         <v>19.256085000000002</v>
       </c>
     </row>
     <row r="70" spans="4:12">
-      <c r="D70" s="17"/>
+      <c r="D70" s="11"/>
       <c r="E70" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="26">
         <v>4.4626029999999997</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="26">
         <v>7.6685369999999997</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="26">
         <v>7.8141699999999998</v>
       </c>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8">
+      <c r="I70" s="26"/>
+      <c r="J70" s="26">
         <v>-0.18829699999999999</v>
       </c>
-      <c r="K70" s="8">
+      <c r="K70" s="26">
         <v>9.4133000000000008E-2</v>
       </c>
-      <c r="L70" s="8">
+      <c r="L70" s="26">
         <v>0.11462699999999999</v>
       </c>
     </row>
     <row r="71" spans="4:12">
-      <c r="D71" s="18"/>
+      <c r="D71" s="12"/>
       <c r="E71" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="25">
         <v>22.055130999999999</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="25">
         <v>44.558721000000006</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H71" s="25">
         <v>48.112253000000003</v>
       </c>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7">
+      <c r="I71" s="25"/>
+      <c r="J71" s="25">
         <v>21.347904999999997</v>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="25">
         <v>32.861454999999999</v>
       </c>
-      <c r="L71" s="7">
+      <c r="L71" s="25">
         <v>19.141458</v>
       </c>
     </row>
     <row r="72" spans="4:12" ht="42">
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="10" t="s">
         <v>80</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="26">
         <v>318.63</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="26">
         <v>313.91000000000003</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="26">
         <v>318.14</v>
       </c>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8">
+      <c r="I72" s="26"/>
+      <c r="J72" s="26">
         <v>11.09</v>
       </c>
-      <c r="K72" s="8">
+      <c r="K72" s="26">
         <v>80.37</v>
       </c>
-      <c r="L72" s="8">
+      <c r="L72" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="4:12" ht="28">
-      <c r="D73" s="17"/>
+      <c r="D73" s="11"/>
       <c r="E73" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="26">
         <v>39.163350999999999</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="26">
         <v>52.201753000000004</v>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="26">
         <v>80.52843</v>
       </c>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8">
+      <c r="I73" s="26"/>
+      <c r="J73" s="26">
         <v>-3.9457720000000003</v>
       </c>
-      <c r="K73" s="8">
+      <c r="K73" s="26">
         <v>-15.284420000000001</v>
       </c>
-      <c r="L73" s="8">
+      <c r="L73" s="26">
         <v>0.45628400000000002</v>
       </c>
     </row>
     <row r="74" spans="4:12" ht="28">
-      <c r="D74" s="17"/>
+      <c r="D74" s="11"/>
       <c r="E74" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="26">
         <v>-37.376781000000001</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="26">
         <v>-21.157933</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="26">
         <v>-15.863934</v>
       </c>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8">
+      <c r="I74" s="26"/>
+      <c r="J74" s="26">
         <v>13.248953</v>
       </c>
-      <c r="K74" s="8">
+      <c r="K74" s="26">
         <v>32.589048999999996</v>
       </c>
-      <c r="L74" s="8">
+      <c r="L74" s="26">
         <v>18.821306</v>
       </c>
     </row>
     <row r="75" spans="4:12" ht="28">
-      <c r="D75" s="17"/>
+      <c r="D75" s="11"/>
       <c r="E75" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="26">
         <v>1.00274</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="26">
         <v>-35.759923999999998</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="26">
         <v>-64.492998999999998</v>
       </c>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8">
+      <c r="I75" s="26"/>
+      <c r="J75" s="26">
         <v>-9.2973710000000001</v>
       </c>
-      <c r="K75" s="8">
+      <c r="K75" s="26">
         <v>-17.265646</v>
       </c>
-      <c r="L75" s="8">
+      <c r="L75" s="26">
         <v>-18.653129</v>
       </c>
     </row>
     <row r="76" spans="4:12">
-      <c r="D76" s="18"/>
+      <c r="D76" s="12"/>
       <c r="E76" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="25">
         <v>18.811067999999999</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G76" s="25">
         <v>14.080121999999999</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H76" s="25">
         <v>14.21599</v>
       </c>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7">
+      <c r="I76" s="25"/>
+      <c r="J76" s="25">
         <v>5.3400999999999997E-2</v>
       </c>
-      <c r="K76" s="7">
+      <c r="K76" s="25">
         <v>9.2383000000000007E-2</v>
       </c>
-      <c r="L76" s="7">
+      <c r="L76" s="25">
         <v>0.71684499999999995</v>
       </c>
     </row>
     <row r="77" spans="4:12">
-      <c r="D77" s="16" t="s">
+      <c r="D77" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="27">
         <v>0.57779999999999998</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="27">
         <v>0.52739999999999998</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77" s="27">
         <v>0.45400000000000001</v>
       </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9">
+      <c r="I77" s="27"/>
+      <c r="J77" s="27">
         <v>1E-4</v>
       </c>
-      <c r="K77" s="9">
+      <c r="K77" s="27">
         <v>1.14E-2</v>
       </c>
-      <c r="L77" s="9">
+      <c r="L77" s="27">
         <v>9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="78" spans="4:12">
-      <c r="D78" s="17"/>
+      <c r="D78" s="11"/>
       <c r="E78" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78" s="28">
         <v>0.87</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G78" s="28">
         <v>0.98</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="28">
         <v>1</v>
       </c>
-      <c r="I78" s="11"/>
-      <c r="J78" s="10">
+      <c r="I78" s="29"/>
+      <c r="J78" s="28">
         <v>23.94</v>
       </c>
-      <c r="K78" s="10">
+      <c r="K78" s="28">
         <v>6.58</v>
       </c>
-      <c r="L78" s="10">
+      <c r="L78" s="28">
         <v>28.53</v>
       </c>
     </row>
     <row r="79" spans="4:12">
-      <c r="D79" s="17"/>
+      <c r="D79" s="11"/>
       <c r="E79" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79" s="28">
         <v>0.38</v>
       </c>
-      <c r="G79" s="10">
+      <c r="G79" s="28">
         <v>0.48</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="28">
         <v>0.51</v>
       </c>
-      <c r="I79" s="11"/>
-      <c r="J79" s="10">
+      <c r="I79" s="29"/>
+      <c r="J79" s="28">
         <v>22.4</v>
       </c>
-      <c r="K79" s="10">
+      <c r="K79" s="28">
         <v>5.64</v>
       </c>
-      <c r="L79" s="10">
+      <c r="L79" s="28">
         <v>28.47</v>
       </c>
     </row>
     <row r="80" spans="4:12" ht="28">
-      <c r="D80" s="17"/>
+      <c r="D80" s="11"/>
       <c r="E80" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="30">
         <f t="shared" ref="F80:G80" si="0">F54/AVERAGE(E7,F7)</f>
         <v>57.060260637957441</v>
       </c>
-      <c r="G80" s="12">
+      <c r="G80" s="30">
         <f t="shared" si="0"/>
         <v>70.358084112061746</v>
       </c>
-      <c r="H80" s="12">
+      <c r="H80" s="30">
         <f>H54/AVERAGE(G7,H7)</f>
         <v>77.235755919851911</v>
       </c>
-      <c r="I80" s="12"/>
-      <c r="J80" s="10">
-        <v>0</v>
-      </c>
-      <c r="K80" s="10">
+      <c r="I80" s="30"/>
+      <c r="J80" s="28">
+        <v>0</v>
+      </c>
+      <c r="K80" s="28">
         <v>1.98</v>
       </c>
-      <c r="L80" s="10">
+      <c r="L80" s="28">
         <v>281.56</v>
       </c>
     </row>
     <row r="81" spans="4:12">
-      <c r="D81" s="17"/>
+      <c r="D81" s="11"/>
       <c r="E81" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="30">
         <f t="shared" ref="F81:H81" si="1">F55/AVERAGE(E11,F11)</f>
         <v>2.6080365448326397</v>
       </c>
-      <c r="G81" s="12">
+      <c r="G81" s="30">
         <f t="shared" si="1"/>
         <v>2.3469910826047711</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="30">
         <f t="shared" si="1"/>
         <v>2.7859254099048134</v>
       </c>
-      <c r="I81" s="12"/>
-      <c r="J81" s="10">
-        <v>0</v>
-      </c>
-      <c r="K81" s="10">
+      <c r="I81" s="30"/>
+      <c r="J81" s="28">
+        <v>0</v>
+      </c>
+      <c r="K81" s="28">
         <v>2.42</v>
       </c>
-      <c r="L81" s="10"/>
+      <c r="L81" s="28"/>
     </row>
     <row r="82" spans="4:12">
-      <c r="D82" s="17"/>
+      <c r="D82" s="11"/>
       <c r="E82" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="27">
         <v>7.6100000000000001E-2</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="27">
         <v>0.15859999999999999</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82" s="27">
         <v>0.16309999999999999</v>
       </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9">
+      <c r="I82" s="27"/>
+      <c r="J82" s="27">
         <v>2.1756000000000002</v>
       </c>
-      <c r="K82" s="9">
+      <c r="K82" s="27">
         <v>0.4587</v>
       </c>
-      <c r="L82" s="9">
+      <c r="L82" s="27">
         <v>13.0458</v>
       </c>
     </row>
     <row r="83" spans="4:12">
-      <c r="D83" s="17"/>
+      <c r="D83" s="11"/>
       <c r="E83" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="27">
         <v>0.14099999999999999</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="27">
         <v>0.23269999999999999</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83" s="27">
         <v>0.24399999999999999</v>
       </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="9">
+      <c r="I83" s="27"/>
+      <c r="J83" s="27">
         <v>1.32E-2</v>
       </c>
-      <c r="K83" s="9">
+      <c r="K83" s="27">
         <v>1.9199999999999998E-2</v>
       </c>
-      <c r="L83" s="9">
+      <c r="L83" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="4:12">
-      <c r="D84" s="17"/>
+      <c r="D84" s="11"/>
       <c r="E84" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="30">
         <f>SUM(F28,F29,F37)/F54</f>
         <v>0.64065604877710791</v>
       </c>
-      <c r="G84" s="12">
+      <c r="G84" s="30">
         <f t="shared" ref="G84:L84" si="2">SUM(G28,G29,G37)/G54</f>
         <v>0.52988281466315268</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="30">
         <f t="shared" si="2"/>
         <v>0.40653735432729349</v>
       </c>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12">
+      <c r="I84" s="30"/>
+      <c r="J84" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K84" s="12">
+      <c r="K84" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L84" s="12">
+      <c r="L84" s="30">
         <f t="shared" si="2"/>
         <v>4.6391485579845855E-2</v>
       </c>
     </row>
     <row r="85" spans="4:12">
-      <c r="D85" s="18"/>
+      <c r="D85" s="12"/>
       <c r="E85" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="30">
         <f>F72/F54</f>
         <v>1.099680769192168</v>
       </c>
-      <c r="G85" s="12">
+      <c r="G85" s="30">
         <f t="shared" ref="G85:L85" si="3">G72/G54</f>
         <v>1.1175379143454449</v>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="30">
         <f t="shared" si="3"/>
         <v>1.0783619063704393</v>
       </c>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12">
+      <c r="I85" s="30"/>
+      <c r="J85" s="30">
         <f t="shared" si="3"/>
         <v>1.1302091661492064</v>
       </c>
-      <c r="K85" s="12">
+      <c r="K85" s="30">
         <f t="shared" si="3"/>
         <v>1.1218338814015982</v>
       </c>
-      <c r="L85" s="12">
+      <c r="L85" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="D54:D71"/>
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D85"/>
     <mergeCell ref="D1:E2"/>
@@ -3189,7 +3120,6 @@
     <mergeCell ref="D3:D25"/>
     <mergeCell ref="D26:D44"/>
     <mergeCell ref="D45:D53"/>
-    <mergeCell ref="D54:D71"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3202,10 +3132,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="4:9">
-      <c r="D1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="27"/>
+      <c r="D1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="21"/>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3220,7 +3150,7 @@
       </c>
     </row>
     <row r="2" spans="4:9">
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="22" t="s">
         <v>97</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -3232,7 +3162,7 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="4:9">
-      <c r="D3" s="29"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="2" t="s">
         <v>79</v>
       </c>
@@ -3242,7 +3172,7 @@
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="4:9">
-      <c r="D4" s="29"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="2" t="s">
         <v>93</v>
       </c>
@@ -3252,7 +3182,7 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="4:9">
-      <c r="D5" s="30"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="2" t="s">
         <v>92</v>
       </c>
@@ -3262,7 +3192,7 @@
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="4:9">
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -3274,7 +3204,7 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="4:9">
-      <c r="D7" s="29"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3284,7 +3214,7 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="4:9">
-      <c r="D8" s="29"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
@@ -3294,7 +3224,7 @@
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="4:9">
-      <c r="D9" s="29"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
@@ -3304,7 +3234,7 @@
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="4:9">
-      <c r="D10" s="29"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3314,7 +3244,7 @@
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="4:9">
-      <c r="D11" s="29"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="2" t="s">
         <v>23</v>
       </c>
@@ -3324,7 +3254,7 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="4:9">
-      <c r="D12" s="29"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
@@ -3334,7 +3264,7 @@
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="4:9">
-      <c r="D13" s="29"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>99</v>
       </c>
@@ -3344,7 +3274,7 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="4:9" ht="28">
-      <c r="D14" s="29"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
@@ -3354,7 +3284,7 @@
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="4:9">
-      <c r="D15" s="29"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>36</v>
       </c>
@@ -3364,7 +3294,7 @@
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="4:9">
-      <c r="D16" s="29"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
@@ -3374,7 +3304,7 @@
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="4:9">
-      <c r="D17" s="29"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>52</v>
       </c>
@@ -3384,7 +3314,7 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="4:9">
-      <c r="D18" s="29"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>87</v>
       </c>
@@ -3394,7 +3324,7 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="4:9" ht="28">
-      <c r="D19" s="29"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>101</v>
       </c>
@@ -3404,7 +3334,7 @@
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="4:9">
-      <c r="D20" s="30"/>
+      <c r="D20" s="24"/>
       <c r="E20" s="2" t="s">
         <v>102</v>
       </c>
@@ -3414,7 +3344,7 @@
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="4:9" ht="28">
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="22" t="s">
         <v>103</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -3426,7 +3356,7 @@
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="4:9" ht="42">
-      <c r="D22" s="29"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="2" t="s">
         <v>81</v>
       </c>
@@ -3436,7 +3366,7 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="4:9">
-      <c r="D23" s="30"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="2" t="s">
         <v>95</v>
       </c>
@@ -3455,207 +3385,4 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43521169-F013-3040-9ABC-4628A30D5BEC}">
-  <dimension ref="H14:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="14" spans="8:16">
-      <c r="H14" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-    </row>
-    <row r="15" spans="8:16">
-      <c r="H15" s="31"/>
-      <c r="I15" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="M15" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="N15" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="P15" s="32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="8:16">
-      <c r="H16" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-    </row>
-    <row r="17" spans="8:16">
-      <c r="H17" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-    </row>
-    <row r="18" spans="8:16" ht="28">
-      <c r="H18" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-    </row>
-    <row r="19" spans="8:16" ht="28">
-      <c r="H19" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-    </row>
-    <row r="20" spans="8:16">
-      <c r="H20" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-    </row>
-    <row r="21" spans="8:16" ht="28">
-      <c r="H21" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-    </row>
-    <row r="22" spans="8:16">
-      <c r="H22" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-    </row>
-    <row r="23" spans="8:16">
-      <c r="H23" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-    </row>
-    <row r="24" spans="8:16">
-      <c r="H24" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-    </row>
-    <row r="25" spans="8:16">
-      <c r="H25" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-    </row>
-    <row r="26" spans="8:16">
-      <c r="H26" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="M14:P14"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>